--- a/data/SOK-Amsterdam-Asfalt-2026-calculatie.xlsx
+++ b/data/SOK-Amsterdam-Asfalt-2026-calculatie.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Tarieven" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Locaties" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Per werksoort" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Per weg" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Per asfaltsoort" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Per weg" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,9 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="€ #,##0;(€ #,##0);-"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;-#,##0.00;-"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -102,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -114,8 +116,13 @@
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -481,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
@@ -571,147 +578,223 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Kolom 'Waarom deze werksoort' op het blad Locaties zegt per regel waar de indeling vandaan komt.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Maatvoering</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>De schouwer noteert vrij: '4.00 x 1.40 + 1.80 x 2.00', '2x 2.20 x 0.45', 'Lengte 3,05 Breedte 1,81'.</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Asfaltsoort — rood of zwart</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Alle varianten zijn omgerekend naar vlakken, en daaruit volgt het oppervlak.</t>
+          <t>Rood of zwart zegt waar het werk in zit, niet hoe het wordt uitgevoerd: zowel rood als zwart</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Gecontroleerd tegen de eigen totalen van het rapport: 5,5 m2 en 4,1 m2 komen exact uit.</t>
+          <t>asfalt kan met de hotbox of machinaal. Het is dus een aparte kolom, geen werksoort.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>10 van de 156 meldingen noemen geen enkele maat; die hebben geen oppervlak.</t>
+          <t>Het rapport noemt de asfaltsoort alleen bij de herstelpunten van de nutsbedrijven —</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>8 x zwart (rijweg) en 1 x rood (fiets-/voetpad). Bij de overige 147 staat het er niet,</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Tarieven</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>en dan blijft de kolom leeg. Zie het blad Per asfaltsoort voor de percentages.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>De blauwe cellen op het blad Tarieven zijn invoer — pas ze aan naar je eigen prijspeil.</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>De startwaarden zijn de CROW-kostenkengetallen uit crow_kosten.py en zijn een orde van</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Foto's</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>grootte, geen offerte. Alle bedragen in dit werkboek rekenen daarop door.</t>
+          <t>De foto's komen uit het digitale rapport, niet uit de scan. Waar de schouwer meer dan een</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>foto maakte staan ze allemaal in een genummerd blad, in dezelfde volgorde als zijn tekst</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Let op</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>('foto 1', 'foto 3'). Kolom 'Aantal foto's' zegt hoeveel opnames er per locatie zijn.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Baanakkerspad heeft geen GPS in het bronrapport.</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Stellingweg: het adres in het rapport (Ceramiquelaan 723) ligt 3,4 km van de overige</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Maatvoering</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>punten op die straat — coordinaat controleren.</t>
+          <t>De schouwer noteert vrij: '4.00 x 1.40 + 1.80 x 2.00', '2x 2.20 x 0.45', 'Lengte 3,05 Breedte 1,81'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Alle varianten zijn omgerekend naar vlakken, en daaruit volgt het oppervlak.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Openen en controleren</t>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Gecontroleerd tegen de eigen totalen van het rapport: 5,5 m2 en 4,1 m2 komen exact uit.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Dit bestand bevat formules zonder opgeslagen uitkomst. Excel rekent ze bij het openen door;</t>
+          <t>10 van de 156 meldingen noemen geen enkele maat; die hebben geen oppervlak.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>zie je lege cellen, druk dan op F9.</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Tarieven</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Controlegetal: met de starttarieven hoort het totaal op het blad Locaties uit te komen op</t>
+          <t>De blauwe cellen op het blad Tarieven zijn invoer — pas ze aan naar je eigen prijspeil.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>minimaal € 37.584 en maximaal € 89.568. Wijkt dat af, dan is er iets met de formules of zijn</t>
+          <t>De startwaarden zijn de CROW-kostenkengetallen uit crow_kosten.py en zijn een orde van</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>de tarieven aangepast — dat laatste is de bedoeling.</t>
+          <t>grootte, geen offerte. Alle bedragen in dit werkboek rekenen daarop door.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Met de startwaarden komt het totaal uit tussen € 37.584 en € 89.568.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Let op</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Kolom 'Let op' op het blad Locaties markeert elke regel die aandacht vraagt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Baanakkerspad heeft geen GPS in het bronrapport.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Stellingweg: het adres in het rapport (Ceramiquelaan 723) ligt 3,4 km van de overige</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>punten op die straat — coordinaat controleren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Bijwerken</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Dit werkboek is gegenereerd uit data/sok_amsterdam_asfalt_2026.json met</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>scripts/maak_calculatie_excel.py. Verandert de dataset, draai dat script opnieuw.</t>
         </is>
       </c>
     </row>
@@ -726,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -842,74 +925,28 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Asfalt zwart (rijweg)</t>
+          <t>Asfalt – nog in te delen</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>plek</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>€150–400 / plek</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Asfalt rood (fiets-/voetpad)</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>plek</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>€150–400 / plek</t>
+          <t>geen tarief — werksoort nog niet bepaald</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Asfalt – nog in te delen</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>geen tarief — werksoort nog niet bepaald</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Startwaarden: CROW-kostenkengetallen (crow_kosten.py). Orde van grootte, geen offerte.</t>
         </is>
@@ -926,7 +963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y159"/>
+  <dimension ref="A1:AD159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -954,6 +991,11 @@
     <col width="34" customWidth="1" min="23" max="23"/>
     <col width="9" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
+    <col width="44" customWidth="1" min="26" max="26"/>
+    <col width="52" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1082,6 +1124,31 @@
           <t>Foto</t>
         </is>
       </c>
+      <c r="Z1" s="6" t="inlineStr">
+        <is>
+          <t>Waarom deze werksoort</t>
+        </is>
+      </c>
+      <c r="AA1" s="6" t="inlineStr">
+        <is>
+          <t>Let op</t>
+        </is>
+      </c>
+      <c r="AB1" s="6" t="inlineStr">
+        <is>
+          <t>Asset-code (weg)</t>
+        </is>
+      </c>
+      <c r="AC1" s="6" t="inlineStr">
+        <is>
+          <t>Asfaltsoort</t>
+        </is>
+      </c>
+      <c r="AD1" s="6" t="inlineStr">
+        <is>
+          <t>Aantal foto's</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1127,7 +1194,7 @@
         <v>2.28</v>
       </c>
       <c r="K2" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B2,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B2,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L2" s="7">
@@ -1135,11 +1202,11 @@
         <v/>
       </c>
       <c r="M2" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B2,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B2,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N2" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B2,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B2,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O2" s="8">
@@ -1189,6 +1256,21 @@
           <t>001-oostzanerdijk.jpg</t>
         </is>
       </c>
+      <c r="Z2" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA2" s="9" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-OOSTZANERDIJK</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1234,7 +1316,7 @@
         <v>2.4</v>
       </c>
       <c r="K3" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B3,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B3,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L3" s="7">
@@ -1242,11 +1324,11 @@
         <v/>
       </c>
       <c r="M3" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B3,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B3,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N3" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B3,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B3,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O3" s="8">
@@ -1295,6 +1377,21 @@
         <is>
           <t>002-oostzanerdijk.jpg</t>
         </is>
+      </c>
+      <c r="Z3" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA3" s="9" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-OOSTZANERDIJK</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1331,7 +1428,7 @@
       <c r="I4" s="7" t="n"/>
       <c r="J4" s="7" t="n"/>
       <c r="K4" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B4,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B4,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L4" s="7">
@@ -1339,11 +1436,11 @@
         <v/>
       </c>
       <c r="M4" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B4,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B4,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N4" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B4,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B4,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O4" s="8">
@@ -1393,6 +1490,25 @@
           <t>003-stellingweg.jpg</t>
         </is>
       </c>
+      <c r="Z4" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA4" s="9" t="inlineStr">
+        <is>
+          <t>Coordinaat ligt 3.4 km van de overige punten op Stellingweg — het adres in het rapport (Céramiquelaan 723, Amsterdam) hoort bij een andere buurt. Controleer dit punt op de kaart. · geen maatvoering in de bron</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-STELLINGWEG</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1438,7 +1554,7 @@
         <v>0.64</v>
       </c>
       <c r="K5" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B5,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B5,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L5" s="7">
@@ -1446,11 +1562,11 @@
         <v/>
       </c>
       <c r="M5" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B5,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B5,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N5" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B5,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B5,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O5" s="8">
@@ -1500,6 +1616,21 @@
           <t>004-stellingweg.jpg</t>
         </is>
       </c>
+      <c r="Z5" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA5" s="9" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-STELLINGWEG</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1541,7 +1672,7 @@
         <v>4.32</v>
       </c>
       <c r="K6" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B6,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B6,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L6" s="7">
@@ -1549,11 +1680,11 @@
         <v/>
       </c>
       <c r="M6" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B6,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B6,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N6" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B6,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B6,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O6" s="8">
@@ -1603,6 +1734,21 @@
           <t>005-stellingweg.jpg</t>
         </is>
       </c>
+      <c r="Z6" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA6" s="9" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-STELLINGWEG</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1648,7 +1794,7 @@
         <v>8.44</v>
       </c>
       <c r="K7" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B7,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B7,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L7" s="7">
@@ -1656,11 +1802,11 @@
         <v/>
       </c>
       <c r="M7" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B7,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B7,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N7" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B7,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B7,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O7" s="8">
@@ -1710,6 +1856,21 @@
           <t>006-zuideinde.jpg</t>
         </is>
       </c>
+      <c r="Z7" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA7" s="9" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ZUIDEINDE</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1751,7 +1912,7 @@
         <v>2.38</v>
       </c>
       <c r="K8" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B8,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B8,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L8" s="7">
@@ -1759,11 +1920,11 @@
         <v/>
       </c>
       <c r="M8" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B8,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B8,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N8" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B8,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B8,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O8" s="8">
@@ -1813,6 +1974,21 @@
           <t>007-zuideinde.jpg</t>
         </is>
       </c>
+      <c r="Z8" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA8" s="9" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ZUIDEINDE</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1854,7 +2030,7 @@
         <v>1.1</v>
       </c>
       <c r="K9" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B9,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B9,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L9" s="7">
@@ -1862,11 +2038,11 @@
         <v/>
       </c>
       <c r="M9" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B9,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B9,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N9" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B9,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B9,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O9" s="8">
@@ -1916,6 +2092,21 @@
           <t>008-zuideinde.jpg</t>
         </is>
       </c>
+      <c r="Z9" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA9" s="9" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ZUIDEINDE</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1961,7 +2152,7 @@
         <v>5.04</v>
       </c>
       <c r="K10" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B10,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B10,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L10" s="7">
@@ -1969,11 +2160,11 @@
         <v/>
       </c>
       <c r="M10" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B10,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B10,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N10" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B10,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B10,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O10" s="8">
@@ -2023,6 +2214,21 @@
           <t>009-zuideinde.jpg</t>
         </is>
       </c>
+      <c r="Z10" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA10" s="9" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ZUIDEINDE</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2068,7 +2274,7 @@
         <v>2.04</v>
       </c>
       <c r="K11" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B11,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B11,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L11" s="7">
@@ -2076,11 +2282,11 @@
         <v/>
       </c>
       <c r="M11" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B11,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B11,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N11" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B11,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B11,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O11" s="8">
@@ -2130,6 +2336,21 @@
           <t>010-zuideinde.jpg</t>
         </is>
       </c>
+      <c r="Z11" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA11" s="9" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ZUIDEINDE</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2175,7 +2396,7 @@
         <v>5.18</v>
       </c>
       <c r="K12" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B12,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B12,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L12" s="7">
@@ -2183,11 +2404,11 @@
         <v/>
       </c>
       <c r="M12" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B12,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B12,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N12" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B12,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B12,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O12" s="8">
@@ -2237,6 +2458,21 @@
           <t>011-zuideinde.jpg</t>
         </is>
       </c>
+      <c r="Z12" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA12" s="9" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ZUIDEINDE</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2282,7 +2518,7 @@
         <v>2.5</v>
       </c>
       <c r="K13" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B13,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B13,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L13" s="7">
@@ -2290,11 +2526,11 @@
         <v/>
       </c>
       <c r="M13" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B13,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B13,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N13" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B13,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B13,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O13" s="8">
@@ -2341,8 +2577,23 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>012-cornelis-roosstraat.jpg</t>
-        </is>
+          <t>012-cornelisroosstraat.jpg</t>
+        </is>
+      </c>
+      <c r="Z13" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA13" s="9" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-CORNELIS-ROOSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2389,7 +2640,7 @@
         <v>3.3</v>
       </c>
       <c r="K14" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B14,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B14,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L14" s="7">
@@ -2397,11 +2648,11 @@
         <v/>
       </c>
       <c r="M14" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B14,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B14,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N14" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B14,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B14,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O14" s="8">
@@ -2448,8 +2699,23 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>013-cornelis-roosstraat.jpg</t>
-        </is>
+          <t>013-cornelisroosstraat.jpg</t>
+        </is>
+      </c>
+      <c r="Z14" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA14" s="9" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-CORNELIS-ROOSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2496,7 +2762,7 @@
         <v>4.4</v>
       </c>
       <c r="K15" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B15,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B15,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L15" s="7">
@@ -2504,11 +2770,11 @@
         <v/>
       </c>
       <c r="M15" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B15,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B15,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N15" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B15,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B15,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O15" s="8">
@@ -2555,8 +2821,23 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>014-cornelis-roosstraat.jpg</t>
-        </is>
+          <t>014-cornelisroosstraat.jpg</t>
+        </is>
+      </c>
+      <c r="Z15" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA15" s="9" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-CORNELIS-ROOSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2603,7 +2884,7 @@
         <v>2</v>
       </c>
       <c r="K16" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B16,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B16,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L16" s="7">
@@ -2611,11 +2892,11 @@
         <v/>
       </c>
       <c r="M16" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B16,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B16,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N16" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B16,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B16,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O16" s="8">
@@ -2662,8 +2943,23 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>015-cornelis-roosstraat.jpg</t>
-        </is>
+          <t>015-cornelisroosstraat.jpg</t>
+        </is>
+      </c>
+      <c r="Z16" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA16" s="9" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-CORNELIS-ROOSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2710,7 +3006,7 @@
         <v>20.88</v>
       </c>
       <c r="K17" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B17,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B17,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L17" s="7">
@@ -2718,11 +3014,11 @@
         <v/>
       </c>
       <c r="M17" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B17,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B17,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N17" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B17,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B17,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O17" s="8">
@@ -2772,6 +3068,21 @@
           <t>016-molenwijk.jpg</t>
         </is>
       </c>
+      <c r="Z17" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA17" s="9" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-MOLENWIJK</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2817,7 +3128,7 @@
         <v>150</v>
       </c>
       <c r="K18" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B18,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B18,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L18" s="7">
@@ -2825,11 +3136,11 @@
         <v/>
       </c>
       <c r="M18" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B18,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B18,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N18" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B18,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B18,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O18" s="8">
@@ -2876,8 +3187,23 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>017-sportpark-oostzanerwerf.jpg</t>
-        </is>
+          <t>017-sportparkoostzanerwerf.jpg</t>
+        </is>
+      </c>
+      <c r="Z18" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA18" s="9" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-SPORTPARK-OOSTZANERWERF</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2924,7 +3250,7 @@
         <v>18</v>
       </c>
       <c r="K19" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B19,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B19,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L19" s="7">
@@ -2932,11 +3258,11 @@
         <v/>
       </c>
       <c r="M19" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B19,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B19,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N19" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B19,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B19,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O19" s="8">
@@ -2986,6 +3312,21 @@
           <t>018-oostzanerdijk.jpg</t>
         </is>
       </c>
+      <c r="Z19" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA19" s="9" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-OOSTZANERDIJK</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3031,7 +3372,7 @@
         <v>2</v>
       </c>
       <c r="K20" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B20,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B20,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L20" s="7">
@@ -3039,11 +3380,11 @@
         <v/>
       </c>
       <c r="M20" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B20,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B20,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N20" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B20,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B20,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O20" s="8">
@@ -3085,13 +3426,28 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>6/49</t>
+          <t>7/49</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>019-molenaarsweg.jpg</t>
         </is>
+      </c>
+      <c r="Z20" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA20" s="9" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-MOLENAARSWEG</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -3138,7 +3494,7 @@
         <v>9</v>
       </c>
       <c r="K21" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B21,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B21,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L21" s="7">
@@ -3146,11 +3502,11 @@
         <v/>
       </c>
       <c r="M21" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B21,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B21,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N21" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B21,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B21,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O21" s="8">
@@ -3199,6 +3555,21 @@
         <is>
           <t>020-molenaarsweg.jpg</t>
         </is>
+      </c>
+      <c r="Z21" s="9" t="inlineStr">
+        <is>
+          <t>in het rapport groen doorgestreept — werksoort onduidelijk</t>
+        </is>
+      </c>
+      <c r="AA21" s="9" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-MOLENAARSWEG</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -3235,7 +3606,7 @@
       <c r="I22" s="7" t="n"/>
       <c r="J22" s="7" t="n"/>
       <c r="K22" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B22,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B22,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L22" s="7">
@@ -3243,11 +3614,11 @@
         <v/>
       </c>
       <c r="M22" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B22,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B22,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N22" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B22,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B22,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O22" s="8">
@@ -3297,6 +3668,25 @@
           <t>021-molenaarsweg.jpg</t>
         </is>
       </c>
+      <c r="Z22" s="9" t="inlineStr">
+        <is>
+          <t>in het rapport groen doorgestreept — werksoort onduidelijk</t>
+        </is>
+      </c>
+      <c r="AA22" s="9" t="inlineStr">
+        <is>
+          <t>geen maatvoering in de bron</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-MOLENAARSWEG</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3342,7 +3732,7 @@
         <v>5.69</v>
       </c>
       <c r="K23" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B23,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B23,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L23" s="7">
@@ -3350,11 +3740,11 @@
         <v/>
       </c>
       <c r="M23" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B23,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B23,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N23" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B23,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B23,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O23" s="8">
@@ -3404,6 +3794,21 @@
           <t>022-meteorenweg.jpg</t>
         </is>
       </c>
+      <c r="Z23" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA23" s="9" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-METEORENWEG</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3449,7 +3854,7 @@
         <v>51</v>
       </c>
       <c r="K24" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B24,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B24,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L24" s="7">
@@ -3457,11 +3862,11 @@
         <v/>
       </c>
       <c r="M24" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B24,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B24,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N24" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B24,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B24,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O24" s="8">
@@ -3510,6 +3915,21 @@
         <is>
           <t>023-aldebaranstraat.jpg</t>
         </is>
+      </c>
+      <c r="Z24" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA24" s="9" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ALDEBARANSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -3546,7 +3966,7 @@
       <c r="I25" s="7" t="n"/>
       <c r="J25" s="7" t="n"/>
       <c r="K25" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B25,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B25,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L25" s="7">
@@ -3554,11 +3974,11 @@
         <v/>
       </c>
       <c r="M25" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B25,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B25,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N25" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B25,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B25,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O25" s="8">
@@ -3608,6 +4028,25 @@
           <t>024-aldebaranstraat.jpg</t>
         </is>
       </c>
+      <c r="Z25" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA25" s="9" t="inlineStr">
+        <is>
+          <t>geen maatvoering in de bron</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ALDEBARANSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3653,7 +4092,7 @@
         <v>0.72</v>
       </c>
       <c r="K26" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B26,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B26,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L26" s="7">
@@ -3661,11 +4100,11 @@
         <v/>
       </c>
       <c r="M26" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B26,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B26,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N26" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B26,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B26,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O26" s="8">
@@ -3707,13 +4146,28 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>8/49</t>
+          <t>9/49</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
           <t>025-rigelstraat.jpg</t>
         </is>
+      </c>
+      <c r="Z26" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA26" s="9" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-RIGELSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -3760,7 +4214,7 @@
         <v>22.05</v>
       </c>
       <c r="K27" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B27,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B27,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L27" s="7">
@@ -3768,11 +4222,11 @@
         <v/>
       </c>
       <c r="M27" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B27,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B27,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N27" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B27,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B27,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O27" s="8">
@@ -3822,6 +4276,21 @@
           <t>026-rigelstraat.jpg</t>
         </is>
       </c>
+      <c r="Z27" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA27" s="9" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-RIGELSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3867,7 +4336,7 @@
         <v>44.26</v>
       </c>
       <c r="K28" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B28,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B28,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L28" s="7">
@@ -3875,11 +4344,11 @@
         <v/>
       </c>
       <c r="M28" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B28,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B28,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N28" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B28,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B28,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O28" s="8">
@@ -3929,6 +4398,21 @@
           <t>027-zonneweg.jpg</t>
         </is>
       </c>
+      <c r="Z28" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA28" s="9" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ZONNEWEG</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3974,7 +4458,7 @@
         <v>6.3</v>
       </c>
       <c r="K29" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B29,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B29,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L29" s="7">
@@ -3982,11 +4466,11 @@
         <v/>
       </c>
       <c r="M29" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B29,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B29,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N29" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B29,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B29,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O29" s="8">
@@ -4028,13 +4512,28 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>9/49</t>
+          <t>10/49</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>028-meteorenweg.jpg</t>
         </is>
+      </c>
+      <c r="Z29" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA29" s="9" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-METEORENWEG</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -4081,7 +4580,7 @@
         <v>21.54</v>
       </c>
       <c r="K30" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B30,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B30,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L30" s="7">
@@ -4089,11 +4588,11 @@
         <v/>
       </c>
       <c r="M30" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B30,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B30,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N30" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B30,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B30,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O30" s="8">
@@ -4143,6 +4642,21 @@
           <t>029-kometensingel.jpg</t>
         </is>
       </c>
+      <c r="Z30" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA30" s="9" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KOMETENSINGEL</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -4188,7 +4702,7 @@
         <v>4</v>
       </c>
       <c r="K31" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B31,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B31,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L31" s="7">
@@ -4196,11 +4710,11 @@
         <v/>
       </c>
       <c r="M31" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B31,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B31,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N31" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B31,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B31,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O31" s="8">
@@ -4250,6 +4764,21 @@
           <t>030-kometensingel.jpg</t>
         </is>
       </c>
+      <c r="Z31" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA31" s="9" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KOMETENSINGEL</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -4295,7 +4824,7 @@
         <v>1.17</v>
       </c>
       <c r="K32" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B32,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B32,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L32" s="7">
@@ -4303,11 +4832,11 @@
         <v/>
       </c>
       <c r="M32" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B32,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B32,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N32" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B32,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B32,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O32" s="8">
@@ -4357,6 +4886,21 @@
           <t>031-meteorenweg.jpg</t>
         </is>
       </c>
+      <c r="Z32" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA32" s="9" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-METEORENWEG</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -4402,7 +4946,7 @@
         <v>105.5</v>
       </c>
       <c r="K33" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B33,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B33,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L33" s="7">
@@ -4410,11 +4954,11 @@
         <v/>
       </c>
       <c r="M33" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B33,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B33,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N33" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B33,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B33,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O33" s="8">
@@ -4464,6 +5008,21 @@
           <t>032-neptunusstraat.jpg</t>
         </is>
       </c>
+      <c r="Z33" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA33" s="9" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-NEPTUNUSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -4509,7 +5068,7 @@
         <v>1.74</v>
       </c>
       <c r="K34" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B34,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B34,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L34" s="7">
@@ -4517,11 +5076,11 @@
         <v/>
       </c>
       <c r="M34" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B34,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B34,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N34" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B34,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B34,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O34" s="8">
@@ -4563,13 +5122,28 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>11/49</t>
+          <t>12/49</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
           <t>033-neptunusstraat.jpg</t>
         </is>
+      </c>
+      <c r="Z34" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA34" s="9" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-NEPTUNUSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -4616,7 +5190,7 @@
         <v>0.96</v>
       </c>
       <c r="K35" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B35,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B35,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L35" s="7">
@@ -4624,11 +5198,11 @@
         <v/>
       </c>
       <c r="M35" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B35,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B35,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N35" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B35,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B35,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O35" s="8">
@@ -4678,6 +5252,21 @@
           <t>034-neptunusstraat.jpg</t>
         </is>
       </c>
+      <c r="Z35" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA35" s="9" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-NEPTUNUSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -4723,7 +5312,7 @@
         <v>9.15</v>
       </c>
       <c r="K36" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B36,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B36,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L36" s="7">
@@ -4731,11 +5320,11 @@
         <v/>
       </c>
       <c r="M36" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B36,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B36,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N36" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B36,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B36,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O36" s="8">
@@ -4784,6 +5373,21 @@
         <is>
           <t>035-neptunusstraat.jpg</t>
         </is>
+      </c>
+      <c r="Z36" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA36" s="9" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-NEPTUNUSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -4820,7 +5424,7 @@
       <c r="I37" s="7" t="n"/>
       <c r="J37" s="7" t="n"/>
       <c r="K37" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B37,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B37,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L37" s="7">
@@ -4828,11 +5432,11 @@
         <v/>
       </c>
       <c r="M37" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B37,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B37,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N37" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B37,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B37,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O37" s="8">
@@ -4882,6 +5486,25 @@
           <t>036-uranusstraat.jpg</t>
         </is>
       </c>
+      <c r="Z37" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA37" s="9" t="inlineStr">
+        <is>
+          <t>geen maatvoering in de bron</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-URANUSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -4927,7 +5550,7 @@
         <v>16.11</v>
       </c>
       <c r="K38" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B38,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B38,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L38" s="7">
@@ -4935,11 +5558,11 @@
         <v/>
       </c>
       <c r="M38" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B38,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B38,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N38" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B38,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B38,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O38" s="8">
@@ -4989,6 +5612,21 @@
           <t>037-mercuriusstraat.jpg</t>
         </is>
       </c>
+      <c r="Z38" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA38" s="9" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-MERCURIUSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -5034,7 +5672,7 @@
         <v>24.64</v>
       </c>
       <c r="K39" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B39,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B39,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L39" s="7">
@@ -5042,11 +5680,11 @@
         <v/>
       </c>
       <c r="M39" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B39,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B39,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N39" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B39,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B39,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O39" s="8">
@@ -5096,6 +5734,21 @@
           <t>038-saturnusstraat.jpg</t>
         </is>
       </c>
+      <c r="Z39" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA39" s="9" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-SATURNUSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -5141,7 +5794,7 @@
         <v>1.98</v>
       </c>
       <c r="K40" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B40,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B40,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L40" s="7">
@@ -5149,11 +5802,11 @@
         <v/>
       </c>
       <c r="M40" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B40,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B40,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N40" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B40,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B40,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O40" s="8">
@@ -5203,6 +5856,21 @@
           <t>039-marsstraat.jpg</t>
         </is>
       </c>
+      <c r="Z40" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA40" s="9" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-MARSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -5248,7 +5916,7 @@
         <v>8.1</v>
       </c>
       <c r="K41" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B41,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B41,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L41" s="7">
@@ -5256,11 +5924,11 @@
         <v/>
       </c>
       <c r="M41" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B41,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B41,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N41" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B41,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B41,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O41" s="8">
@@ -5310,6 +5978,21 @@
           <t>040-marsstraat.jpg</t>
         </is>
       </c>
+      <c r="Z41" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA41" s="9" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-MARSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -5355,7 +6038,7 @@
         <v>12.7</v>
       </c>
       <c r="K42" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B42,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B42,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L42" s="7">
@@ -5363,11 +6046,11 @@
         <v/>
       </c>
       <c r="M42" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B42,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B42,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N42" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B42,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B42,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O42" s="8">
@@ -5417,6 +6100,21 @@
           <t>041-marsstraat.jpg</t>
         </is>
       </c>
+      <c r="Z42" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA42" s="9" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-MARSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -5462,7 +6160,7 @@
         <v>60.8</v>
       </c>
       <c r="K43" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B43,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B43,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L43" s="7">
@@ -5470,11 +6168,11 @@
         <v/>
       </c>
       <c r="M43" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B43,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B43,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N43" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B43,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B43,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O43" s="8">
@@ -5524,6 +6222,21 @@
           <t>042-saturnusstraat.jpg</t>
         </is>
       </c>
+      <c r="Z43" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA43" s="9" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-SATURNUSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -5569,7 +6282,7 @@
         <v>7.56</v>
       </c>
       <c r="K44" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B44,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B44,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L44" s="7">
@@ -5577,11 +6290,11 @@
         <v/>
       </c>
       <c r="M44" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B44,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B44,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N44" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B44,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B44,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O44" s="8">
@@ -5631,6 +6344,21 @@
           <t>043-jupiterstraat.jpg</t>
         </is>
       </c>
+      <c r="Z44" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA44" s="9" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-JUPITERSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -5676,7 +6404,7 @@
         <v>20.96</v>
       </c>
       <c r="K45" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B45,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B45,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L45" s="7">
@@ -5684,11 +6412,11 @@
         <v/>
       </c>
       <c r="M45" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B45,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B45,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N45" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B45,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B45,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O45" s="8">
@@ -5738,6 +6466,21 @@
           <t>044-uranusstraat.jpg</t>
         </is>
       </c>
+      <c r="Z45" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA45" s="9" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-URANUSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -5783,7 +6526,7 @@
         <v>8.6</v>
       </c>
       <c r="K46" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B46,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B46,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L46" s="7">
@@ -5791,11 +6534,11 @@
         <v/>
       </c>
       <c r="M46" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B46,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B46,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N46" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B46,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B46,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O46" s="8">
@@ -5845,6 +6588,21 @@
           <t>045-kometensingel.jpg</t>
         </is>
       </c>
+      <c r="Z46" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA46" s="9" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KOMETENSINGEL</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -5890,7 +6648,7 @@
         <v>12.61</v>
       </c>
       <c r="K47" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B47,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B47,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L47" s="7">
@@ -5898,11 +6656,11 @@
         <v/>
       </c>
       <c r="M47" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B47,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B47,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N47" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B47,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B47,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O47" s="8">
@@ -5952,6 +6710,21 @@
           <t>046-mercuriusstraat.jpg</t>
         </is>
       </c>
+      <c r="Z47" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA47" s="9" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-MERCURIUSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -5997,7 +6770,7 @@
         <v>22.77</v>
       </c>
       <c r="K48" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B48,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B48,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L48" s="7">
@@ -6005,11 +6778,11 @@
         <v/>
       </c>
       <c r="M48" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B48,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B48,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N48" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B48,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B48,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O48" s="8">
@@ -6059,6 +6832,21 @@
           <t>047-mercuriusstraat.jpg</t>
         </is>
       </c>
+      <c r="Z48" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA48" s="9" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-MERCURIUSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -6104,7 +6892,7 @@
         <v>13.76</v>
       </c>
       <c r="K49" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B49,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B49,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L49" s="7">
@@ -6112,11 +6900,11 @@
         <v/>
       </c>
       <c r="M49" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B49,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B49,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N49" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B49,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B49,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O49" s="8">
@@ -6166,6 +6954,21 @@
           <t>048-kometensingel.jpg</t>
         </is>
       </c>
+      <c r="Z49" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA49" s="9" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KOMETENSINGEL</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -6211,7 +7014,7 @@
         <v>4.14</v>
       </c>
       <c r="K50" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B50,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B50,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L50" s="7">
@@ -6219,11 +7022,11 @@
         <v/>
       </c>
       <c r="M50" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B50,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B50,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N50" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B50,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B50,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O50" s="8">
@@ -6273,6 +7076,21 @@
           <t>049-kometensingel.jpg</t>
         </is>
       </c>
+      <c r="Z50" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA50" s="9" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KOMETENSINGEL</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -6318,7 +7136,7 @@
         <v>4.32</v>
       </c>
       <c r="K51" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B51,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B51,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L51" s="7">
@@ -6326,11 +7144,11 @@
         <v/>
       </c>
       <c r="M51" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B51,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B51,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N51" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B51,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B51,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O51" s="8">
@@ -6377,8 +7195,23 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>050-grote-beerstraat.jpg</t>
-        </is>
+          <t>050-grotebeerstraat.jpg</t>
+        </is>
+      </c>
+      <c r="Z51" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA51" s="9" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-GROTE-BEERSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -6425,7 +7258,7 @@
         <v>7.56</v>
       </c>
       <c r="K52" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B52,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B52,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L52" s="7">
@@ -6433,11 +7266,11 @@
         <v/>
       </c>
       <c r="M52" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B52,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B52,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N52" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B52,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B52,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O52" s="8">
@@ -6487,6 +7320,21 @@
           <t>051-aldebaranplein.jpg</t>
         </is>
       </c>
+      <c r="Z52" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA52" s="9" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ALDEBARANPLEIN</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -6532,7 +7380,7 @@
         <v>1.47</v>
       </c>
       <c r="K53" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B53,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B53,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L53" s="7">
@@ -6540,11 +7388,11 @@
         <v/>
       </c>
       <c r="M53" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B53,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B53,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N53" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B53,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B53,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O53" s="8">
@@ -6594,6 +7442,21 @@
           <t>052-castorplein.jpg</t>
         </is>
       </c>
+      <c r="Z53" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA53" s="9" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-CASTORPLEIN</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -6639,7 +7502,7 @@
         <v>3.68</v>
       </c>
       <c r="K54" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B54,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B54,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L54" s="7">
@@ -6647,11 +7510,11 @@
         <v/>
       </c>
       <c r="M54" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B54,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B54,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N54" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B54,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B54,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O54" s="8">
@@ -6701,6 +7564,21 @@
           <t>053-meteorensingel.jpg</t>
         </is>
       </c>
+      <c r="Z54" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA54" s="9" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-METEORENSINGEL</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -6746,7 +7624,7 @@
         <v>24.78</v>
       </c>
       <c r="K55" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B55,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B55,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L55" s="7">
@@ -6754,11 +7632,11 @@
         <v/>
       </c>
       <c r="M55" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B55,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B55,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N55" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B55,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B55,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O55" s="8">
@@ -6808,6 +7686,21 @@
           <t>054-kometensingel.jpg</t>
         </is>
       </c>
+      <c r="Z55" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA55" s="9" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KOMETENSINGEL</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -6853,7 +7746,7 @@
         <v>10</v>
       </c>
       <c r="K56" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B56,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B56,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L56" s="7">
@@ -6861,11 +7754,11 @@
         <v/>
       </c>
       <c r="M56" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B56,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B56,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N56" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B56,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B56,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O56" s="8">
@@ -6915,6 +7808,21 @@
           <t>055-kometensingel.jpg</t>
         </is>
       </c>
+      <c r="Z56" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA56" s="9" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KOMETENSINGEL</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -6960,7 +7868,7 @@
         <v>1.05</v>
       </c>
       <c r="K57" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B57,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B57,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L57" s="7">
@@ -6968,11 +7876,11 @@
         <v/>
       </c>
       <c r="M57" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B57,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B57,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N57" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B57,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B57,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O57" s="8">
@@ -7022,6 +7930,21 @@
           <t>056-kometensingel.jpg</t>
         </is>
       </c>
+      <c r="Z57" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA57" s="9" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KOMETENSINGEL</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -7067,7 +7990,7 @@
         <v>17.16</v>
       </c>
       <c r="K58" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B58,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B58,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L58" s="7">
@@ -7075,11 +7998,11 @@
         <v/>
       </c>
       <c r="M58" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B58,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B58,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N58" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B58,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B58,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O58" s="8">
@@ -7126,8 +8049,23 @@
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>057-kleine-zonneplein.jpg</t>
-        </is>
+          <t>057-kleinezonneplein.jpg</t>
+        </is>
+      </c>
+      <c r="Z58" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA58" s="9" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KLEINE-ZONNEPLEIN</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -7174,7 +8112,7 @@
         <v>6.27</v>
       </c>
       <c r="K59" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B59,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B59,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L59" s="7">
@@ -7182,11 +8120,11 @@
         <v/>
       </c>
       <c r="M59" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B59,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B59,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N59" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B59,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B59,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O59" s="8">
@@ -7236,6 +8174,21 @@
           <t>058-zonneplein.jpg</t>
         </is>
       </c>
+      <c r="Z59" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA59" s="9" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ZONNEPLEIN</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -7281,7 +8234,7 @@
         <v>2.48</v>
       </c>
       <c r="K60" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B60,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B60,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L60" s="7">
@@ -7289,11 +8242,11 @@
         <v/>
       </c>
       <c r="M60" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B60,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B60,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N60" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B60,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B60,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O60" s="8">
@@ -7340,8 +8293,23 @@
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>059-kleine-beerstraat.jpg</t>
-        </is>
+          <t>059-kleinebeerstraat.jpg</t>
+        </is>
+      </c>
+      <c r="Z60" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA60" s="9" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KLEINE-BEERSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -7388,7 +8356,7 @@
         <v>16.14</v>
       </c>
       <c r="K61" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B61,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B61,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L61" s="7">
@@ -7396,11 +8364,11 @@
         <v/>
       </c>
       <c r="M61" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B61,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B61,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N61" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B61,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B61,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O61" s="8">
@@ -7450,6 +8418,21 @@
           <t>060-planetenplein.jpg</t>
         </is>
       </c>
+      <c r="Z61" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA61" s="9" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-PLANETENPLEIN</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -7495,7 +8478,7 @@
         <v>1.32</v>
       </c>
       <c r="K62" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B62,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B62,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L62" s="7">
@@ -7503,11 +8486,11 @@
         <v/>
       </c>
       <c r="M62" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B62,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B62,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N62" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B62,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B62,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O62" s="8">
@@ -7557,6 +8540,21 @@
           <t>061-maanstraat.jpg</t>
         </is>
       </c>
+      <c r="Z62" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA62" s="9" t="inlineStr"/>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-MAANSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -7602,7 +8600,7 @@
         <v>3.8</v>
       </c>
       <c r="K63" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B63,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B63,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L63" s="7">
@@ -7610,11 +8608,11 @@
         <v/>
       </c>
       <c r="M63" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B63,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B63,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N63" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B63,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B63,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O63" s="8">
@@ -7664,6 +8662,21 @@
           <t>062-maanstraat.jpg</t>
         </is>
       </c>
+      <c r="Z63" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA63" s="9" t="inlineStr"/>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-MAANSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -7709,7 +8722,7 @@
         <v>21.06</v>
       </c>
       <c r="K64" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B64,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B64,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L64" s="7">
@@ -7717,11 +8730,11 @@
         <v/>
       </c>
       <c r="M64" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B64,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B64,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N64" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B64,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B64,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O64" s="8">
@@ -7771,6 +8784,21 @@
           <t>063-maanstraat.jpg</t>
         </is>
       </c>
+      <c r="Z64" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA64" s="9" t="inlineStr"/>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-MAANSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -7816,7 +8844,7 @@
         <v>102</v>
       </c>
       <c r="K65" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B65,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B65,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L65" s="7">
@@ -7824,11 +8852,11 @@
         <v/>
       </c>
       <c r="M65" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B65,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B65,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N65" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B65,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B65,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O65" s="8">
@@ -7878,6 +8906,21 @@
           <t>064-orionplantsoen.jpg</t>
         </is>
       </c>
+      <c r="Z65" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA65" s="9" t="inlineStr"/>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ORIONPLANTSOEN</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -7923,7 +8966,7 @@
         <v>11.34</v>
       </c>
       <c r="K66" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B66,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B66,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L66" s="7">
@@ -7931,11 +8974,11 @@
         <v/>
       </c>
       <c r="M66" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B66,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B66,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N66" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B66,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B66,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O66" s="8">
@@ -7985,6 +9028,21 @@
           <t>065-maanstraat.jpg</t>
         </is>
       </c>
+      <c r="Z66" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA66" s="9" t="inlineStr"/>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-MAANSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -8030,7 +9088,7 @@
         <v>22.98</v>
       </c>
       <c r="K67" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B67,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B67,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L67" s="7">
@@ -8038,11 +9096,11 @@
         <v/>
       </c>
       <c r="M67" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B67,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B67,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N67" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B67,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B67,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O67" s="8">
@@ -8092,6 +9150,21 @@
           <t>066-rigelstraat.jpg</t>
         </is>
       </c>
+      <c r="Z67" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA67" s="9" t="inlineStr"/>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-RIGELSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -8133,7 +9206,7 @@
         <v>9.9</v>
       </c>
       <c r="K68" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B68,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B68,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L68" s="7">
@@ -8141,11 +9214,11 @@
         <v/>
       </c>
       <c r="M68" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B68,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B68,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N68" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B68,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B68,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O68" s="8">
@@ -8195,6 +9268,21 @@
           <t>067-rigelstraat.jpg</t>
         </is>
       </c>
+      <c r="Z68" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA68" s="9" t="inlineStr"/>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-RIGELSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -8240,7 +9328,7 @@
         <v>13.68</v>
       </c>
       <c r="K69" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B69,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B69,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L69" s="7">
@@ -8248,11 +9336,11 @@
         <v/>
       </c>
       <c r="M69" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B69,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B69,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N69" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B69,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B69,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O69" s="8">
@@ -8302,6 +9390,21 @@
           <t>068-rigelstraat.jpg</t>
         </is>
       </c>
+      <c r="Z69" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA69" s="9" t="inlineStr"/>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-RIGELSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -8347,7 +9450,7 @@
         <v>18.84</v>
       </c>
       <c r="K70" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B70,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B70,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L70" s="7">
@@ -8355,11 +9458,11 @@
         <v/>
       </c>
       <c r="M70" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B70,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B70,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N70" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B70,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B70,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O70" s="8">
@@ -8409,6 +9512,21 @@
           <t>069-orionplantsoen.jpg</t>
         </is>
       </c>
+      <c r="Z70" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA70" s="9" t="inlineStr"/>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ORIONPLANTSOEN</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -8450,7 +9568,7 @@
         <v>7.2</v>
       </c>
       <c r="K71" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B71,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B71,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L71" s="7">
@@ -8458,11 +9576,11 @@
         <v/>
       </c>
       <c r="M71" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B71,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B71,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N71" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B71,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B71,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O71" s="8">
@@ -8512,6 +9630,21 @@
           <t>070-orionplantsoen.jpg</t>
         </is>
       </c>
+      <c r="Z71" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA71" s="9" t="inlineStr"/>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ORIONPLANTSOEN</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -8557,7 +9690,7 @@
         <v>62.2</v>
       </c>
       <c r="K72" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B72,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B72,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L72" s="7">
@@ -8565,11 +9698,11 @@
         <v/>
       </c>
       <c r="M72" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B72,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B72,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N72" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B72,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B72,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O72" s="8">
@@ -8619,6 +9752,21 @@
           <t>071-orionstraat.jpg</t>
         </is>
       </c>
+      <c r="Z72" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA72" s="9" t="inlineStr"/>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ORIONSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -8664,7 +9812,7 @@
         <v>1.86</v>
       </c>
       <c r="K73" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B73,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B73,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L73" s="7">
@@ -8672,11 +9820,11 @@
         <v/>
       </c>
       <c r="M73" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B73,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B73,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N73" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B73,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B73,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O73" s="8">
@@ -8726,6 +9874,21 @@
           <t>072-orionplantsoen.jpg</t>
         </is>
       </c>
+      <c r="Z73" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA73" s="9" t="inlineStr"/>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ORIONPLANTSOEN</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -8771,7 +9934,7 @@
         <v>2.86</v>
       </c>
       <c r="K74" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B74,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B74,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L74" s="7">
@@ -8779,11 +9942,11 @@
         <v/>
       </c>
       <c r="M74" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B74,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B74,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N74" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B74,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B74,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O74" s="8">
@@ -8833,6 +9996,21 @@
           <t>073-kometensingel.jpg</t>
         </is>
       </c>
+      <c r="Z74" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA74" s="9" t="inlineStr"/>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KOMETENSINGEL</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -8878,7 +10056,7 @@
         <v>3.6</v>
       </c>
       <c r="K75" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B75,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B75,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L75" s="7">
@@ -8886,11 +10064,11 @@
         <v/>
       </c>
       <c r="M75" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B75,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B75,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N75" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B75,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B75,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O75" s="8">
@@ -8940,6 +10118,21 @@
           <t>074-argostraat.jpg</t>
         </is>
       </c>
+      <c r="Z75" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA75" s="9" t="inlineStr"/>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ARGOSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -8985,7 +10178,7 @@
         <v>1.26</v>
       </c>
       <c r="K76" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B76,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B76,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L76" s="7">
@@ -8993,11 +10186,11 @@
         <v/>
       </c>
       <c r="M76" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B76,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B76,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N76" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B76,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B76,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O76" s="8">
@@ -9047,6 +10240,21 @@
           <t>075-argostraat.jpg</t>
         </is>
       </c>
+      <c r="Z76" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA76" s="9" t="inlineStr"/>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ARGOSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -9092,7 +10300,7 @@
         <v>4.08</v>
       </c>
       <c r="K77" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B77,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B77,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L77" s="7">
@@ -9100,11 +10308,11 @@
         <v/>
       </c>
       <c r="M77" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B77,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B77,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N77" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B77,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B77,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O77" s="8">
@@ -9154,6 +10362,21 @@
           <t>076-planetenstraat.jpg</t>
         </is>
       </c>
+      <c r="Z77" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA77" s="9" t="inlineStr"/>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-PLANETENSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -9199,7 +10422,7 @@
         <v>15.73</v>
       </c>
       <c r="K78" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B78,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B78,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L78" s="7">
@@ -9207,11 +10430,11 @@
         <v/>
       </c>
       <c r="M78" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B78,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B78,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N78" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B78,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B78,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O78" s="8">
@@ -9261,6 +10484,21 @@
           <t>077-argostraat.jpg</t>
         </is>
       </c>
+      <c r="Z78" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA78" s="9" t="inlineStr"/>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ARGOSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -9306,7 +10544,7 @@
         <v>3.43</v>
       </c>
       <c r="K79" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B79,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B79,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L79" s="7">
@@ -9314,11 +10552,11 @@
         <v/>
       </c>
       <c r="M79" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B79,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B79,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N79" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B79,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B79,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O79" s="8">
@@ -9368,6 +10606,21 @@
           <t>078-aldebaranstraat.jpg</t>
         </is>
       </c>
+      <c r="Z79" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA79" s="9" t="inlineStr"/>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ALDEBARANSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -9413,7 +10666,7 @@
         <v>6.4</v>
       </c>
       <c r="K80" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B80,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B80,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L80" s="7">
@@ -9421,11 +10674,11 @@
         <v/>
       </c>
       <c r="M80" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B80,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B80,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N80" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B80,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B80,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O80" s="8">
@@ -9475,6 +10728,21 @@
           <t>079-koppelingpad.jpg</t>
         </is>
       </c>
+      <c r="Z80" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA80" s="9" t="inlineStr"/>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KOPPELINGPAD</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -9520,7 +10788,7 @@
         <v>5.8</v>
       </c>
       <c r="K81" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B81,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B81,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L81" s="7">
@@ -9528,11 +10796,11 @@
         <v/>
       </c>
       <c r="M81" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B81,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B81,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N81" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B81,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B81,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O81" s="8">
@@ -9582,6 +10850,21 @@
           <t>080-koppelingpad.jpg</t>
         </is>
       </c>
+      <c r="Z81" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA81" s="9" t="inlineStr"/>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KOPPELINGPAD</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -9627,7 +10910,7 @@
         <v>6.22</v>
       </c>
       <c r="K82" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B82,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B82,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L82" s="7">
@@ -9635,11 +10918,11 @@
         <v/>
       </c>
       <c r="M82" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B82,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B82,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N82" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B82,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B82,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O82" s="8">
@@ -9689,6 +10972,21 @@
           <t>081-koppelingpad.jpg</t>
         </is>
       </c>
+      <c r="Z82" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA82" s="9" t="inlineStr"/>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KOPPELINGPAD</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -9734,7 +11032,7 @@
         <v>2.55</v>
       </c>
       <c r="K83" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B83,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B83,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L83" s="7">
@@ -9742,11 +11040,11 @@
         <v/>
       </c>
       <c r="M83" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B83,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B83,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N83" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B83,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B83,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O83" s="8">
@@ -9796,6 +11094,21 @@
           <t>082-scheepsbouwweg.jpg</t>
         </is>
       </c>
+      <c r="Z83" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA83" s="9" t="inlineStr"/>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-SCHEEPSBOUWWEG</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -9841,7 +11154,7 @@
         <v>3.27</v>
       </c>
       <c r="K84" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B84,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B84,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L84" s="7">
@@ -9849,11 +11162,11 @@
         <v/>
       </c>
       <c r="M84" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B84,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B84,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N84" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B84,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B84,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O84" s="8">
@@ -9903,6 +11216,21 @@
           <t>083-scheepsbouwweg.jpg</t>
         </is>
       </c>
+      <c r="Z84" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA84" s="9" t="inlineStr"/>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-SCHEEPSBOUWWEG</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -9948,7 +11276,7 @@
         <v>2.9</v>
       </c>
       <c r="K85" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B85,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B85,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L85" s="7">
@@ -9956,11 +11284,11 @@
         <v/>
       </c>
       <c r="M85" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B85,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B85,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N85" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B85,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B85,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O85" s="8">
@@ -10010,6 +11338,21 @@
           <t>084-pomonastraat.jpg</t>
         </is>
       </c>
+      <c r="Z85" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA85" s="9" t="inlineStr"/>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-POMONASTRAAT</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -10055,7 +11398,7 @@
         <v>2.9</v>
       </c>
       <c r="K86" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B86,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B86,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L86" s="7">
@@ -10063,11 +11406,11 @@
         <v/>
       </c>
       <c r="M86" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B86,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B86,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N86" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B86,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B86,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O86" s="8">
@@ -10117,6 +11460,21 @@
           <t>085-pomonastraat.jpg</t>
         </is>
       </c>
+      <c r="Z86" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA86" s="9" t="inlineStr"/>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-POMONASTRAAT</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -10162,7 +11520,7 @@
         <v>5.8</v>
       </c>
       <c r="K87" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B87,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B87,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L87" s="7">
@@ -10170,11 +11528,11 @@
         <v/>
       </c>
       <c r="M87" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B87,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B87,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N87" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B87,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B87,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O87" s="8">
@@ -10224,6 +11582,21 @@
           <t>086-pomonastraat.jpg</t>
         </is>
       </c>
+      <c r="Z87" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA87" s="9" t="inlineStr"/>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-POMONASTRAAT</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -10269,7 +11642,7 @@
         <v>1.74</v>
       </c>
       <c r="K88" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B88,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B88,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L88" s="7">
@@ -10277,11 +11650,11 @@
         <v/>
       </c>
       <c r="M88" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B88,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B88,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N88" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B88,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B88,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O88" s="8">
@@ -10331,6 +11704,21 @@
           <t>087-pomonastraat.jpg</t>
         </is>
       </c>
+      <c r="Z88" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA88" s="9" t="inlineStr"/>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-POMONASTRAAT</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -10376,7 +11764,7 @@
         <v>1.8</v>
       </c>
       <c r="K89" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B89,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B89,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L89" s="7">
@@ -10384,11 +11772,11 @@
         <v/>
       </c>
       <c r="M89" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B89,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B89,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N89" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B89,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B89,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O89" s="8">
@@ -10438,6 +11826,21 @@
           <t>088-appelweg.jpg</t>
         </is>
       </c>
+      <c r="Z89" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA89" s="9" t="inlineStr"/>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-APPELWEG</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -10483,7 +11886,7 @@
         <v>10.88</v>
       </c>
       <c r="K90" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B90,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B90,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L90" s="7">
@@ -10491,11 +11894,11 @@
         <v/>
       </c>
       <c r="M90" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B90,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B90,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N90" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B90,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B90,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O90" s="8">
@@ -10544,6 +11947,21 @@
         <is>
           <t>089-perenpad.jpg</t>
         </is>
+      </c>
+      <c r="Z90" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA90" s="9" t="inlineStr"/>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-PERENPAD</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -10580,7 +11998,7 @@
       <c r="I91" s="7" t="n"/>
       <c r="J91" s="7" t="n"/>
       <c r="K91" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B91,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B91,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L91" s="7">
@@ -10588,11 +12006,11 @@
         <v/>
       </c>
       <c r="M91" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B91,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B91,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N91" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B91,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B91,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O91" s="8">
@@ -10641,6 +12059,25 @@
         <is>
           <t>090-molenaarsweg.jpg</t>
         </is>
+      </c>
+      <c r="Z91" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA91" s="9" t="inlineStr">
+        <is>
+          <t>geen maatvoering in de bron</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-MOLENAARSWEG</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -10677,7 +12114,7 @@
       <c r="I92" s="7" t="n"/>
       <c r="J92" s="7" t="n"/>
       <c r="K92" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B92,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B92,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L92" s="7">
@@ -10685,11 +12122,11 @@
         <v/>
       </c>
       <c r="M92" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B92,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B92,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N92" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B92,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B92,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O92" s="8">
@@ -10739,6 +12176,25 @@
           <t>091-kometensingel.jpg</t>
         </is>
       </c>
+      <c r="Z92" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA92" s="9" t="inlineStr">
+        <is>
+          <t>geen maatvoering in de bron</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KOMETENSINGEL</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -10784,7 +12240,7 @@
         <v>3.61</v>
       </c>
       <c r="K93" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B93,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B93,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L93" s="7">
@@ -10792,11 +12248,11 @@
         <v/>
       </c>
       <c r="M93" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B93,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B93,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N93" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B93,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B93,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O93" s="8">
@@ -10846,6 +12302,21 @@
           <t>092-kometensingel.jpg</t>
         </is>
       </c>
+      <c r="Z93" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA93" s="9" t="inlineStr"/>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KOMETENSINGEL</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -10891,7 +12362,7 @@
         <v>0.95</v>
       </c>
       <c r="K94" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B94,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B94,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L94" s="7">
@@ -10899,11 +12370,11 @@
         <v/>
       </c>
       <c r="M94" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B94,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B94,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N94" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B94,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B94,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O94" s="8">
@@ -10953,6 +12424,21 @@
           <t>093-scheepsbouwweg.jpg</t>
         </is>
       </c>
+      <c r="Z94" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA94" s="9" t="inlineStr"/>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-SCHEEPSBOUWWEG</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -10998,7 +12484,7 @@
         <v>87.40000000000001</v>
       </c>
       <c r="K95" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B95,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B95,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L95" s="7">
@@ -11006,11 +12492,11 @@
         <v/>
       </c>
       <c r="M95" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B95,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B95,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N95" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B95,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B95,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O95" s="8">
@@ -11060,6 +12546,21 @@
           <t>094-scheepsbouwweg.jpg</t>
         </is>
       </c>
+      <c r="Z95" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA95" s="9" t="inlineStr"/>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-SCHEEPSBOUWWEG</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -11105,7 +12606,7 @@
         <v>1.8</v>
       </c>
       <c r="K96" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B96,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B96,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L96" s="7">
@@ -11113,11 +12614,11 @@
         <v/>
       </c>
       <c r="M96" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B96,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B96,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N96" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B96,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B96,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O96" s="8">
@@ -11167,6 +12668,21 @@
           <t>095-buiksloterdijk.jpg</t>
         </is>
       </c>
+      <c r="Z96" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA96" s="9" t="inlineStr"/>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-BUIKSLOTERDIJK</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -11212,7 +12728,7 @@
         <v>16</v>
       </c>
       <c r="K97" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B97,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B97,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L97" s="7">
@@ -11220,11 +12736,11 @@
         <v/>
       </c>
       <c r="M97" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B97,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B97,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N97" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B97,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B97,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O97" s="8">
@@ -11274,6 +12790,21 @@
           <t>096-buiksloterdijk.jpg</t>
         </is>
       </c>
+      <c r="Z97" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA97" s="9" t="inlineStr"/>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-BUIKSLOTERDIJK</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -11319,7 +12850,7 @@
         <v>4.8</v>
       </c>
       <c r="K98" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B98,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B98,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L98" s="7">
@@ -11327,11 +12858,11 @@
         <v/>
       </c>
       <c r="M98" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B98,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B98,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N98" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B98,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B98,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O98" s="8">
@@ -11381,6 +12912,21 @@
           <t>097-buiksloterdijk.jpg</t>
         </is>
       </c>
+      <c r="Z98" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA98" s="9" t="inlineStr"/>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-BUIKSLOTERDIJK</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -11426,7 +12972,7 @@
         <v>2.56</v>
       </c>
       <c r="K99" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B99,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B99,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L99" s="7">
@@ -11434,11 +12980,11 @@
         <v/>
       </c>
       <c r="M99" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B99,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B99,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N99" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B99,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B99,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O99" s="8">
@@ -11488,6 +13034,21 @@
           <t>098-buiksloterdijk.jpg</t>
         </is>
       </c>
+      <c r="Z99" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA99" s="9" t="inlineStr"/>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-BUIKSLOTERDIJK</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -11533,7 +13094,7 @@
         <v>11.16</v>
       </c>
       <c r="K100" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B100,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B100,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L100" s="7">
@@ -11541,11 +13102,11 @@
         <v/>
       </c>
       <c r="M100" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B100,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B100,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N100" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B100,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B100,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O100" s="8">
@@ -11595,6 +13156,21 @@
           <t>099-buiksloterdijk.jpg</t>
         </is>
       </c>
+      <c r="Z100" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA100" s="9" t="inlineStr"/>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-BUIKSLOTERDIJK</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -11640,7 +13216,7 @@
         <v>5.32</v>
       </c>
       <c r="K101" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B101,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B101,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L101" s="7">
@@ -11648,11 +13224,11 @@
         <v/>
       </c>
       <c r="M101" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B101,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B101,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N101" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B101,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B101,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O101" s="8">
@@ -11702,6 +13278,21 @@
           <t>100-landsmeerderdijk.jpg</t>
         </is>
       </c>
+      <c r="Z101" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA101" s="9" t="inlineStr"/>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-LANDSMEERDERDIJK</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -11747,7 +13338,7 @@
         <v>1.98</v>
       </c>
       <c r="K102" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B102,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B102,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L102" s="7">
@@ -11755,11 +13346,11 @@
         <v/>
       </c>
       <c r="M102" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B102,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B102,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N102" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B102,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B102,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O102" s="8">
@@ -11809,6 +13400,21 @@
           <t>101-landsmeerderdijk.jpg</t>
         </is>
       </c>
+      <c r="Z102" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA102" s="9" t="inlineStr"/>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-LANDSMEERDERDIJK</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -11854,7 +13460,7 @@
         <v>1.45</v>
       </c>
       <c r="K103" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B103,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B103,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L103" s="7">
@@ -11862,11 +13468,11 @@
         <v/>
       </c>
       <c r="M103" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B103,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B103,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N103" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B103,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B103,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O103" s="8">
@@ -11916,6 +13522,21 @@
           <t>102-landsmeerderdijk.jpg</t>
         </is>
       </c>
+      <c r="Z103" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA103" s="9" t="inlineStr"/>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-LANDSMEERDERDIJK</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -11961,7 +13582,7 @@
         <v>31.02</v>
       </c>
       <c r="K104" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B104,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B104,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L104" s="7">
@@ -11969,11 +13590,11 @@
         <v/>
       </c>
       <c r="M104" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B104,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B104,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N104" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B104,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B104,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O104" s="8">
@@ -12023,6 +13644,21 @@
           <t>103-landsmeerderdijk.jpg</t>
         </is>
       </c>
+      <c r="Z104" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA104" s="9" t="inlineStr"/>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-LANDSMEERDERDIJK</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr"/>
+      <c r="AD104" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -12068,7 +13704,7 @@
         <v>4.26</v>
       </c>
       <c r="K105" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B105,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B105,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L105" s="7">
@@ -12076,11 +13712,11 @@
         <v/>
       </c>
       <c r="M105" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B105,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B105,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N105" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B105,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B105,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O105" s="8">
@@ -12130,6 +13766,21 @@
           <t>104-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z105" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA105" s="9" t="inlineStr"/>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr"/>
+      <c r="AD105" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -12175,7 +13826,7 @@
         <v>23.82</v>
       </c>
       <c r="K106" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B106,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B106,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L106" s="7">
@@ -12183,11 +13834,11 @@
         <v/>
       </c>
       <c r="M106" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B106,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B106,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N106" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B106,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B106,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O106" s="8">
@@ -12237,6 +13888,21 @@
           <t>105-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z106" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA106" s="9" t="inlineStr"/>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr"/>
+      <c r="AD106" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -12282,7 +13948,7 @@
         <v>2.1</v>
       </c>
       <c r="K107" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B107,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B107,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L107" s="7">
@@ -12290,11 +13956,11 @@
         <v/>
       </c>
       <c r="M107" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B107,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B107,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N107" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B107,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B107,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O107" s="8">
@@ -12344,6 +14010,21 @@
           <t>106-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z107" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA107" s="9" t="inlineStr"/>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr"/>
+      <c r="AD107" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -12389,7 +14070,7 @@
         <v>12.78</v>
       </c>
       <c r="K108" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B108,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B108,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L108" s="7">
@@ -12397,11 +14078,11 @@
         <v/>
       </c>
       <c r="M108" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B108,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B108,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N108" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B108,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B108,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O108" s="8">
@@ -12451,6 +14132,21 @@
           <t>107-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z108" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA108" s="9" t="inlineStr"/>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr"/>
+      <c r="AD108" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -12496,7 +14192,7 @@
         <v>6.18</v>
       </c>
       <c r="K109" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B109,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B109,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L109" s="7">
@@ -12504,11 +14200,11 @@
         <v/>
       </c>
       <c r="M109" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B109,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B109,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N109" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B109,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B109,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O109" s="8">
@@ -12558,6 +14254,21 @@
           <t>108-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z109" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA109" s="9" t="inlineStr"/>
+      <c r="AB109" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr"/>
+      <c r="AD109" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -12603,7 +14314,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="K110" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B110,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B110,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L110" s="7">
@@ -12611,11 +14322,11 @@
         <v/>
       </c>
       <c r="M110" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B110,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B110,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N110" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B110,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B110,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O110" s="8">
@@ -12665,6 +14376,21 @@
           <t>109-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z110" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA110" s="9" t="inlineStr"/>
+      <c r="AB110" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC110" s="2" t="inlineStr"/>
+      <c r="AD110" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -12710,7 +14436,7 @@
         <v>42.52</v>
       </c>
       <c r="K111" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B111,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B111,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L111" s="7">
@@ -12718,11 +14444,11 @@
         <v/>
       </c>
       <c r="M111" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B111,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B111,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N111" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B111,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B111,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O111" s="8">
@@ -12772,6 +14498,21 @@
           <t>110-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z111" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA111" s="9" t="inlineStr"/>
+      <c r="AB111" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC111" s="2" t="inlineStr"/>
+      <c r="AD111" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -12817,7 +14558,7 @@
         <v>8.960000000000001</v>
       </c>
       <c r="K112" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B112,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B112,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L112" s="7">
@@ -12825,11 +14566,11 @@
         <v/>
       </c>
       <c r="M112" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B112,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B112,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N112" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B112,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B112,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O112" s="8">
@@ -12879,6 +14620,21 @@
           <t>111-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z112" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA112" s="9" t="inlineStr"/>
+      <c r="AB112" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC112" s="2" t="inlineStr"/>
+      <c r="AD112" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -12924,7 +14680,7 @@
         <v>15.26</v>
       </c>
       <c r="K113" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B113,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B113,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L113" s="7">
@@ -12932,11 +14688,11 @@
         <v/>
       </c>
       <c r="M113" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B113,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B113,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N113" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B113,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B113,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O113" s="8">
@@ -12986,6 +14742,21 @@
           <t>112-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z113" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA113" s="9" t="inlineStr"/>
+      <c r="AB113" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC113" s="2" t="inlineStr"/>
+      <c r="AD113" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -13031,7 +14802,7 @@
         <v>0.98</v>
       </c>
       <c r="K114" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B114,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B114,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L114" s="7">
@@ -13039,11 +14810,11 @@
         <v/>
       </c>
       <c r="M114" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B114,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B114,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N114" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B114,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B114,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O114" s="8">
@@ -13093,6 +14864,21 @@
           <t>113-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z114" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA114" s="9" t="inlineStr"/>
+      <c r="AB114" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC114" s="2" t="inlineStr"/>
+      <c r="AD114" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -13138,7 +14924,7 @@
         <v>9.6</v>
       </c>
       <c r="K115" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B115,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B115,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L115" s="7">
@@ -13146,11 +14932,11 @@
         <v/>
       </c>
       <c r="M115" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B115,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B115,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N115" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B115,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B115,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O115" s="8">
@@ -13200,6 +14986,21 @@
           <t>114-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z115" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA115" s="9" t="inlineStr"/>
+      <c r="AB115" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC115" s="2" t="inlineStr"/>
+      <c r="AD115" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -13245,7 +15046,7 @@
         <v>11.84</v>
       </c>
       <c r="K116" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B116,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B116,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L116" s="7">
@@ -13253,11 +15054,11 @@
         <v/>
       </c>
       <c r="M116" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B116,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B116,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N116" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B116,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B116,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O116" s="8">
@@ -13307,6 +15108,21 @@
           <t>115-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z116" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA116" s="9" t="inlineStr"/>
+      <c r="AB116" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC116" s="2" t="inlineStr"/>
+      <c r="AD116" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -13352,7 +15168,7 @@
         <v>104.36</v>
       </c>
       <c r="K117" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B117,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B117,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L117" s="7">
@@ -13360,11 +15176,11 @@
         <v/>
       </c>
       <c r="M117" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B117,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B117,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N117" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B117,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B117,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O117" s="8">
@@ -13406,13 +15222,28 @@
       </c>
       <c r="X117" s="2" t="inlineStr">
         <is>
-          <t>39/49</t>
+          <t>40/49</t>
         </is>
       </c>
       <c r="Y117" s="2" t="inlineStr">
         <is>
           <t>116-kadoelenweg.jpg</t>
         </is>
+      </c>
+      <c r="Z117" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA117" s="9" t="inlineStr"/>
+      <c r="AB117" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC117" s="2" t="inlineStr"/>
+      <c r="AD117" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="118">
@@ -13459,7 +15290,7 @@
         <v>17.36</v>
       </c>
       <c r="K118" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B118,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B118,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L118" s="7">
@@ -13467,11 +15298,11 @@
         <v/>
       </c>
       <c r="M118" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B118,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B118,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N118" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B118,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B118,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O118" s="8">
@@ -13521,6 +15352,21 @@
           <t>117-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z118" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA118" s="9" t="inlineStr"/>
+      <c r="AB118" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC118" s="2" t="inlineStr"/>
+      <c r="AD118" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -13566,7 +15412,7 @@
         <v>5.88</v>
       </c>
       <c r="K119" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B119,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B119,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L119" s="7">
@@ -13574,11 +15420,11 @@
         <v/>
       </c>
       <c r="M119" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B119,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B119,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N119" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B119,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B119,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O119" s="8">
@@ -13628,6 +15474,21 @@
           <t>118-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z119" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA119" s="9" t="inlineStr"/>
+      <c r="AB119" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC119" s="2" t="inlineStr"/>
+      <c r="AD119" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -13673,7 +15534,7 @@
         <v>29.45</v>
       </c>
       <c r="K120" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B120,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B120,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L120" s="7">
@@ -13681,11 +15542,11 @@
         <v/>
       </c>
       <c r="M120" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B120,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B120,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N120" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B120,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B120,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O120" s="8">
@@ -13735,6 +15596,21 @@
           <t>119-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z120" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA120" s="9" t="inlineStr"/>
+      <c r="AB120" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC120" s="2" t="inlineStr"/>
+      <c r="AD120" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -13780,7 +15656,7 @@
         <v>5.78</v>
       </c>
       <c r="K121" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B121,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B121,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L121" s="7">
@@ -13788,11 +15664,11 @@
         <v/>
       </c>
       <c r="M121" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B121,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B121,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N121" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B121,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B121,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O121" s="8">
@@ -13842,6 +15718,21 @@
           <t>120-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z121" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA121" s="9" t="inlineStr"/>
+      <c r="AB121" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC121" s="2" t="inlineStr"/>
+      <c r="AD121" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -13887,7 +15778,7 @@
         <v>26.11</v>
       </c>
       <c r="K122" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B122,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B122,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L122" s="7">
@@ -13895,11 +15786,11 @@
         <v/>
       </c>
       <c r="M122" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B122,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B122,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N122" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B122,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B122,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O122" s="8">
@@ -13949,6 +15840,21 @@
           <t>121-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z122" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA122" s="9" t="inlineStr"/>
+      <c r="AB122" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC122" s="2" t="inlineStr"/>
+      <c r="AD122" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -13994,7 +15900,7 @@
         <v>4.4</v>
       </c>
       <c r="K123" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B123,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B123,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L123" s="7">
@@ -14002,11 +15908,11 @@
         <v/>
       </c>
       <c r="M123" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B123,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B123,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N123" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B123,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B123,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O123" s="8">
@@ -14056,6 +15962,21 @@
           <t>122-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z123" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA123" s="9" t="inlineStr"/>
+      <c r="AB123" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC123" s="2" t="inlineStr"/>
+      <c r="AD123" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -14101,7 +16022,7 @@
         <v>5.28</v>
       </c>
       <c r="K124" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B124,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B124,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L124" s="7">
@@ -14109,11 +16030,11 @@
         <v/>
       </c>
       <c r="M124" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B124,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B124,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N124" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B124,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B124,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O124" s="8">
@@ -14163,6 +16084,21 @@
           <t>123-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z124" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA124" s="9" t="inlineStr"/>
+      <c r="AB124" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC124" s="2" t="inlineStr"/>
+      <c r="AD124" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -14208,7 +16144,7 @@
         <v>2.88</v>
       </c>
       <c r="K125" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B125,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B125,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L125" s="7">
@@ -14216,11 +16152,11 @@
         <v/>
       </c>
       <c r="M125" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B125,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B125,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N125" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B125,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B125,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O125" s="8">
@@ -14270,6 +16206,21 @@
           <t>124-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z125" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA125" s="9" t="inlineStr"/>
+      <c r="AB125" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC125" s="2" t="inlineStr"/>
+      <c r="AD125" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -14315,7 +16266,7 @@
         <v>10.92</v>
       </c>
       <c r="K126" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B126,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B126,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L126" s="7">
@@ -14323,11 +16274,11 @@
         <v/>
       </c>
       <c r="M126" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B126,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B126,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N126" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B126,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B126,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O126" s="8">
@@ -14377,6 +16328,21 @@
           <t>125-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z126" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA126" s="9" t="inlineStr"/>
+      <c r="AB126" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC126" s="2" t="inlineStr"/>
+      <c r="AD126" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -14422,7 +16388,7 @@
         <v>8.82</v>
       </c>
       <c r="K127" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B127,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B127,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L127" s="7">
@@ -14430,11 +16396,11 @@
         <v/>
       </c>
       <c r="M127" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B127,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B127,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N127" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B127,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B127,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O127" s="8">
@@ -14484,6 +16450,21 @@
           <t>126-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z127" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA127" s="9" t="inlineStr"/>
+      <c r="AB127" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC127" s="2" t="inlineStr"/>
+      <c r="AD127" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -14529,7 +16510,7 @@
         <v>9.1</v>
       </c>
       <c r="K128" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B128,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B128,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L128" s="7">
@@ -14537,11 +16518,11 @@
         <v/>
       </c>
       <c r="M128" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B128,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B128,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N128" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B128,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B128,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O128" s="8">
@@ -14591,6 +16572,21 @@
           <t>127-kadoelenweg.jpg</t>
         </is>
       </c>
+      <c r="Z128" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA128" s="9" t="inlineStr"/>
+      <c r="AB128" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-KADOELENWEG</t>
+        </is>
+      </c>
+      <c r="AC128" s="2" t="inlineStr"/>
+      <c r="AD128" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -14636,7 +16632,7 @@
         <v>4.88</v>
       </c>
       <c r="K129" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B129,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B129,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L129" s="7">
@@ -14644,11 +16640,11 @@
         <v/>
       </c>
       <c r="M129" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B129,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B129,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N129" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B129,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B129,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O129" s="8">
@@ -14698,6 +16694,21 @@
           <t>128-papaverweg.jpg</t>
         </is>
       </c>
+      <c r="Z129" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA129" s="9" t="inlineStr"/>
+      <c r="AB129" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-PAPAVERWEG</t>
+        </is>
+      </c>
+      <c r="AC129" s="2" t="inlineStr"/>
+      <c r="AD129" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -14743,7 +16754,7 @@
         <v>6.65</v>
       </c>
       <c r="K130" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B130,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B130,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L130" s="7">
@@ -14751,11 +16762,11 @@
         <v/>
       </c>
       <c r="M130" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B130,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B130,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N130" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B130,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B130,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O130" s="8">
@@ -14805,6 +16816,21 @@
           <t>129-papaverweg.jpg</t>
         </is>
       </c>
+      <c r="Z130" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA130" s="9" t="inlineStr"/>
+      <c r="AB130" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-PAPAVERWEG</t>
+        </is>
+      </c>
+      <c r="AC130" s="2" t="inlineStr"/>
+      <c r="AD130" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -14850,7 +16876,7 @@
         <v>11.75</v>
       </c>
       <c r="K131" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B131,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B131,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L131" s="7">
@@ -14858,11 +16884,11 @@
         <v/>
       </c>
       <c r="M131" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B131,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B131,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N131" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B131,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B131,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O131" s="8">
@@ -14911,6 +16937,21 @@
         <is>
           <t>130-papaverweg.jpg</t>
         </is>
+      </c>
+      <c r="Z131" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA131" s="9" t="inlineStr"/>
+      <c r="AB131" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-PAPAVERWEG</t>
+        </is>
+      </c>
+      <c r="AC131" s="2" t="inlineStr"/>
+      <c r="AD131" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -14947,7 +16988,7 @@
       <c r="I132" s="7" t="n"/>
       <c r="J132" s="7" t="n"/>
       <c r="K132" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B132,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B132,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L132" s="7">
@@ -14955,11 +16996,11 @@
         <v/>
       </c>
       <c r="M132" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B132,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B132,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N132" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B132,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B132,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O132" s="8">
@@ -15009,6 +17050,25 @@
           <t>131-papaverweg.jpg</t>
         </is>
       </c>
+      <c r="Z132" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA132" s="9" t="inlineStr">
+        <is>
+          <t>geen maatvoering in de bron</t>
+        </is>
+      </c>
+      <c r="AB132" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-PAPAVERWEG</t>
+        </is>
+      </c>
+      <c r="AC132" s="2" t="inlineStr"/>
+      <c r="AD132" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -15054,7 +17114,7 @@
         <v>15.6</v>
       </c>
       <c r="K133" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B133,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B133,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L133" s="7">
@@ -15062,11 +17122,11 @@
         <v/>
       </c>
       <c r="M133" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B133,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B133,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N133" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B133,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B133,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O133" s="8">
@@ -15116,6 +17176,21 @@
           <t>132-papaverweg.jpg</t>
         </is>
       </c>
+      <c r="Z133" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA133" s="9" t="inlineStr"/>
+      <c r="AB133" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-PAPAVERWEG</t>
+        </is>
+      </c>
+      <c r="AC133" s="2" t="inlineStr"/>
+      <c r="AD133" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -15161,7 +17236,7 @@
         <v>106</v>
       </c>
       <c r="K134" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B134,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B134,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L134" s="7">
@@ -15169,11 +17244,11 @@
         <v/>
       </c>
       <c r="M134" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B134,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B134,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N134" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B134,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B134,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O134" s="8">
@@ -15223,6 +17298,21 @@
           <t>133-papaverweg.jpg</t>
         </is>
       </c>
+      <c r="Z134" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "AS" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA134" s="9" t="inlineStr"/>
+      <c r="AB134" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-PAPAVERWEG</t>
+        </is>
+      </c>
+      <c r="AC134" s="2" t="inlineStr"/>
+      <c r="AD134" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -15268,7 +17358,7 @@
         <v>2.52</v>
       </c>
       <c r="K135" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B135,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B135,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L135" s="7">
@@ -15276,11 +17366,11 @@
         <v/>
       </c>
       <c r="M135" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B135,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B135,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N135" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B135,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B135,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O135" s="8">
@@ -15330,6 +17420,21 @@
           <t>134-papaverweg.jpg</t>
         </is>
       </c>
+      <c r="Z135" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA135" s="9" t="inlineStr"/>
+      <c r="AB135" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-PAPAVERWEG</t>
+        </is>
+      </c>
+      <c r="AC135" s="2" t="inlineStr"/>
+      <c r="AD135" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -15375,7 +17480,7 @@
         <v>7.2</v>
       </c>
       <c r="K136" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B136,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B136,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L136" s="7">
@@ -15383,11 +17488,11 @@
         <v/>
       </c>
       <c r="M136" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B136,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B136,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N136" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B136,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B136,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O136" s="8">
@@ -15437,6 +17542,21 @@
           <t>135-papaverweg.jpg</t>
         </is>
       </c>
+      <c r="Z136" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA136" s="9" t="inlineStr"/>
+      <c r="AB136" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-PAPAVERWEG</t>
+        </is>
+      </c>
+      <c r="AC136" s="2" t="inlineStr"/>
+      <c r="AD136" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -15482,7 +17602,7 @@
         <v>1.98</v>
       </c>
       <c r="K137" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B137,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B137,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L137" s="7">
@@ -15490,11 +17610,11 @@
         <v/>
       </c>
       <c r="M137" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B137,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B137,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N137" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B137,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B137,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O137" s="8">
@@ -15543,6 +17663,21 @@
         <is>
           <t>136-papaverweg.jpg</t>
         </is>
+      </c>
+      <c r="Z137" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA137" s="9" t="inlineStr"/>
+      <c r="AB137" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-PAPAVERWEG</t>
+        </is>
+      </c>
+      <c r="AC137" s="2" t="inlineStr"/>
+      <c r="AD137" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -15575,7 +17710,7 @@
       <c r="I138" s="7" t="n"/>
       <c r="J138" s="7" t="n"/>
       <c r="K138" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B138,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B138,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L138" s="7">
@@ -15583,11 +17718,11 @@
         <v/>
       </c>
       <c r="M138" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B138,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B138,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N138" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B138,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B138,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O138" s="8">
@@ -15637,6 +17772,25 @@
           <t>137-staghof.jpg</t>
         </is>
       </c>
+      <c r="Z138" s="9" t="inlineStr">
+        <is>
+          <t>in het rapport groen doorgestreept — werksoort onduidelijk</t>
+        </is>
+      </c>
+      <c r="AA138" s="9" t="inlineStr">
+        <is>
+          <t>geen maatvoering in de bron</t>
+        </is>
+      </c>
+      <c r="AB138" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-STAGHOF</t>
+        </is>
+      </c>
+      <c r="AC138" s="2" t="inlineStr"/>
+      <c r="AD138" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -15682,7 +17836,7 @@
         <v>19.46</v>
       </c>
       <c r="K139" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B139,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B139,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L139" s="7">
@@ -15690,11 +17844,11 @@
         <v/>
       </c>
       <c r="M139" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B139,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B139,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N139" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B139,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B139,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O139" s="8">
@@ -15744,6 +17898,21 @@
           <t>138-astasiastraat.jpg</t>
         </is>
       </c>
+      <c r="Z139" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA139" s="9" t="inlineStr"/>
+      <c r="AB139" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ASTASIASTRAAT</t>
+        </is>
+      </c>
+      <c r="AC139" s="2" t="inlineStr"/>
+      <c r="AD139" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -15789,7 +17958,7 @@
         <v>27.5</v>
       </c>
       <c r="K140" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B140,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B140,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L140" s="7">
@@ -15797,11 +17966,11 @@
         <v/>
       </c>
       <c r="M140" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B140,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B140,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N140" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B140,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B140,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O140" s="8">
@@ -15851,6 +18020,21 @@
           <t>139-astasiastraat.jpg</t>
         </is>
       </c>
+      <c r="Z140" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA140" s="9" t="inlineStr"/>
+      <c r="AB140" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ASTASIASTRAAT</t>
+        </is>
+      </c>
+      <c r="AC140" s="2" t="inlineStr"/>
+      <c r="AD140" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -15896,7 +18080,7 @@
         <v>31.6</v>
       </c>
       <c r="K141" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B141,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B141,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L141" s="7">
@@ -15904,11 +18088,11 @@
         <v/>
       </c>
       <c r="M141" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B141,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B141,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N141" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B141,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B141,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O141" s="8">
@@ -15958,6 +18142,21 @@
           <t>140-eudorinastraat.jpg</t>
         </is>
       </c>
+      <c r="Z141" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA141" s="9" t="inlineStr"/>
+      <c r="AB141" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-EUDORINASTRAAT</t>
+        </is>
+      </c>
+      <c r="AC141" s="2" t="inlineStr"/>
+      <c r="AD141" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -15999,7 +18198,7 @@
         <v>1.44</v>
       </c>
       <c r="K142" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B142,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B142,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L142" s="7">
@@ -16007,11 +18206,11 @@
         <v/>
       </c>
       <c r="M142" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B142,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B142,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N142" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B142,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B142,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O142" s="8">
@@ -16061,6 +18260,25 @@
           <t>141-meteorenweg.jpg</t>
         </is>
       </c>
+      <c r="Z142" s="9" t="inlineStr">
+        <is>
+          <t>de tekst noemt "Hotbox werkzaamheden"</t>
+        </is>
+      </c>
+      <c r="AA142" s="9" t="inlineStr">
+        <is>
+          <t>PRIO — met de hand als voorrang aangemerkt</t>
+        </is>
+      </c>
+      <c r="AB142" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-METEORENWEG</t>
+        </is>
+      </c>
+      <c r="AC142" s="2" t="inlineStr"/>
+      <c r="AD142" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -16102,7 +18320,7 @@
         <v>4.29</v>
       </c>
       <c r="K143" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B143,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B143,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L143" s="7">
@@ -16110,11 +18328,11 @@
         <v/>
       </c>
       <c r="M143" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B143,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B143,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N143" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B143,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B143,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O143" s="8">
@@ -16156,6 +18374,25 @@
           <t>142-baanakkerspad.jpg</t>
         </is>
       </c>
+      <c r="Z143" s="9" t="inlineStr">
+        <is>
+          <t>handgeschreven code "HB" in de kantlijn</t>
+        </is>
+      </c>
+      <c r="AA143" s="9" t="inlineStr">
+        <is>
+          <t>geen GPS in de bron — locatie handmatig bepalen</t>
+        </is>
+      </c>
+      <c r="AB143" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-BAANAKKERSPAD</t>
+        </is>
+      </c>
+      <c r="AC143" s="2" t="inlineStr"/>
+      <c r="AD143" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -16165,7 +18402,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Asfalt zwart (rijweg)</t>
+          <t>Asfalt – nog in te delen</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -16197,7 +18434,7 @@
         <v>29.97</v>
       </c>
       <c r="K144" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B144,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B144,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L144" s="7">
@@ -16205,11 +18442,11 @@
         <v/>
       </c>
       <c r="M144" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B144,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B144,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N144" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B144,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B144,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O144" s="8">
@@ -16259,6 +18496,25 @@
           <t>143-volendammerweg.jpg</t>
         </is>
       </c>
+      <c r="Z144" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn; het rapport noemt wel de asfaltsoort maar niet de uitvoering</t>
+        </is>
+      </c>
+      <c r="AA144" s="9" t="inlineStr"/>
+      <c r="AB144" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-VOLENDAMMERWEG</t>
+        </is>
+      </c>
+      <c r="AC144" s="2" t="inlineStr">
+        <is>
+          <t>zwart (rijweg)</t>
+        </is>
+      </c>
+      <c r="AD144" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -16300,7 +18556,7 @@
         <v>5.52</v>
       </c>
       <c r="K145" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B145,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B145,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L145" s="7">
@@ -16308,11 +18564,11 @@
         <v/>
       </c>
       <c r="M145" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B145,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B145,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N145" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B145,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B145,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O145" s="8">
@@ -16361,6 +18617,21 @@
         <is>
           <t>144-buiksloterdijk.jpg</t>
         </is>
+      </c>
+      <c r="Z145" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA145" s="9" t="inlineStr"/>
+      <c r="AB145" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-BUIKSLOTERDIJK</t>
+        </is>
+      </c>
+      <c r="AC145" s="2" t="inlineStr"/>
+      <c r="AD145" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -16393,7 +18664,7 @@
       <c r="I146" s="7" t="n"/>
       <c r="J146" s="7" t="n"/>
       <c r="K146" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B146,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B146,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L146" s="7">
@@ -16401,11 +18672,11 @@
         <v/>
       </c>
       <c r="M146" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B146,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B146,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N146" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B146,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B146,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O146" s="8">
@@ -16455,6 +18726,25 @@
           <t>145-rigelstraat.jpg</t>
         </is>
       </c>
+      <c r="Z146" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA146" s="9" t="inlineStr">
+        <is>
+          <t>geen maatvoering in de bron</t>
+        </is>
+      </c>
+      <c r="AB146" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-RIGELSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC146" s="2" t="inlineStr"/>
+      <c r="AD146" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -16464,7 +18754,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Asfalt zwart (rijweg)</t>
+          <t>Asfalt – nog in te delen</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -16496,7 +18786,7 @@
         <v>1.15</v>
       </c>
       <c r="K147" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B147,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B147,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L147" s="7">
@@ -16504,11 +18794,11 @@
         <v/>
       </c>
       <c r="M147" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B147,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B147,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N147" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B147,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B147,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O147" s="8">
@@ -16558,6 +18848,25 @@
           <t>146-neptunusstraat.jpg</t>
         </is>
       </c>
+      <c r="Z147" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn; het rapport noemt wel de asfaltsoort maar niet de uitvoering</t>
+        </is>
+      </c>
+      <c r="AA147" s="9" t="inlineStr"/>
+      <c r="AB147" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-NEPTUNUSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC147" s="2" t="inlineStr">
+        <is>
+          <t>zwart (rijweg)</t>
+        </is>
+      </c>
+      <c r="AD147" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -16567,7 +18876,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Asfalt zwart (rijweg)</t>
+          <t>Asfalt – nog in te delen</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -16599,7 +18908,7 @@
         <v>4.1</v>
       </c>
       <c r="K148" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B148,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B148,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L148" s="7">
@@ -16607,11 +18916,11 @@
         <v/>
       </c>
       <c r="M148" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B148,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B148,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N148" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B148,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B148,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O148" s="8">
@@ -16661,6 +18970,25 @@
           <t>147-plejadenplein.jpg</t>
         </is>
       </c>
+      <c r="Z148" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn; het rapport noemt wel de asfaltsoort maar niet de uitvoering</t>
+        </is>
+      </c>
+      <c r="AA148" s="9" t="inlineStr"/>
+      <c r="AB148" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-PLEJADENPLEIN</t>
+        </is>
+      </c>
+      <c r="AC148" s="2" t="inlineStr">
+        <is>
+          <t>zwart (rijweg)</t>
+        </is>
+      </c>
+      <c r="AD148" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -16670,7 +18998,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Asfalt zwart (rijweg)</t>
+          <t>Asfalt – nog in te delen</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -16702,7 +19030,7 @@
         <v>6.69</v>
       </c>
       <c r="K149" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B149,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B149,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L149" s="7">
@@ -16710,11 +19038,11 @@
         <v/>
       </c>
       <c r="M149" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B149,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B149,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N149" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B149,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B149,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O149" s="8">
@@ -16764,6 +19092,25 @@
           <t>148-landsmeerderdijk.jpg</t>
         </is>
       </c>
+      <c r="Z149" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn; het rapport noemt wel de asfaltsoort maar niet de uitvoering</t>
+        </is>
+      </c>
+      <c r="AA149" s="9" t="inlineStr"/>
+      <c r="AB149" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-LANDSMEERDERDIJK</t>
+        </is>
+      </c>
+      <c r="AC149" s="2" t="inlineStr">
+        <is>
+          <t>zwart (rijweg)</t>
+        </is>
+      </c>
+      <c r="AD149" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -16773,7 +19120,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Asfalt zwart (rijweg)</t>
+          <t>Asfalt – nog in te delen</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -16805,7 +19152,7 @@
         <v>3.08</v>
       </c>
       <c r="K150" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B150,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B150,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L150" s="7">
@@ -16813,11 +19160,11 @@
         <v/>
       </c>
       <c r="M150" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B150,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B150,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N150" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B150,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B150,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O150" s="8">
@@ -16867,6 +19214,25 @@
           <t>149-buiksloterdijk.jpg</t>
         </is>
       </c>
+      <c r="Z150" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn; het rapport noemt wel de asfaltsoort maar niet de uitvoering</t>
+        </is>
+      </c>
+      <c r="AA150" s="9" t="inlineStr"/>
+      <c r="AB150" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-BUIKSLOTERDIJK</t>
+        </is>
+      </c>
+      <c r="AC150" s="2" t="inlineStr">
+        <is>
+          <t>zwart (rijweg)</t>
+        </is>
+      </c>
+      <c r="AD150" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -16876,7 +19242,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Asfalt rood (fiets-/voetpad)</t>
+          <t>Asfalt – nog in te delen</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -16908,7 +19274,7 @@
         <v>0.67</v>
       </c>
       <c r="K151" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B151,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B151,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L151" s="7">
@@ -16916,11 +19282,11 @@
         <v/>
       </c>
       <c r="M151" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B151,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B151,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N151" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B151,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B151,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O151" s="8">
@@ -16970,6 +19336,25 @@
           <t>150-floraweg.jpg</t>
         </is>
       </c>
+      <c r="Z151" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn; het rapport noemt wel de asfaltsoort maar niet de uitvoering</t>
+        </is>
+      </c>
+      <c r="AA151" s="9" t="inlineStr"/>
+      <c r="AB151" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-FLORAWEG</t>
+        </is>
+      </c>
+      <c r="AC151" s="2" t="inlineStr">
+        <is>
+          <t>rood (fiets-/voetpad)</t>
+        </is>
+      </c>
+      <c r="AD151" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -16979,7 +19364,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Asfalt zwart (rijweg)</t>
+          <t>Asfalt – nog in te delen</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -17011,7 +19396,7 @@
         <v>1.15</v>
       </c>
       <c r="K152" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B152,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B152,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L152" s="7">
@@ -17019,11 +19404,11 @@
         <v/>
       </c>
       <c r="M152" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B152,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B152,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N152" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B152,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B152,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O152" s="8">
@@ -17073,6 +19458,25 @@
           <t>151-neptunusstraat.jpg</t>
         </is>
       </c>
+      <c r="Z152" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn; het rapport noemt wel de asfaltsoort maar niet de uitvoering</t>
+        </is>
+      </c>
+      <c r="AA152" s="9" t="inlineStr"/>
+      <c r="AB152" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-NEPTUNUSSTRAAT</t>
+        </is>
+      </c>
+      <c r="AC152" s="2" t="inlineStr">
+        <is>
+          <t>zwart (rijweg)</t>
+        </is>
+      </c>
+      <c r="AD152" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -17082,7 +19486,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Asfalt zwart (rijweg)</t>
+          <t>Asfalt – nog in te delen</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -17114,7 +19518,7 @@
         <v>6.69</v>
       </c>
       <c r="K153" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B153,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B153,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L153" s="7">
@@ -17122,11 +19526,11 @@
         <v/>
       </c>
       <c r="M153" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B153,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B153,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N153" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B153,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B153,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O153" s="8">
@@ -17176,6 +19580,25 @@
           <t>152-landsmeerderdijk.jpg</t>
         </is>
       </c>
+      <c r="Z153" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn; het rapport noemt wel de asfaltsoort maar niet de uitvoering</t>
+        </is>
+      </c>
+      <c r="AA153" s="9" t="inlineStr"/>
+      <c r="AB153" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-LANDSMEERDERDIJK</t>
+        </is>
+      </c>
+      <c r="AC153" s="2" t="inlineStr">
+        <is>
+          <t>zwart (rijweg)</t>
+        </is>
+      </c>
+      <c r="AD153" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -17185,7 +19608,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Asfalt zwart (rijweg)</t>
+          <t>Asfalt – nog in te delen</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -17217,7 +19640,7 @@
         <v>21.83</v>
       </c>
       <c r="K154" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B154,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B154,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L154" s="7">
@@ -17225,11 +19648,11 @@
         <v/>
       </c>
       <c r="M154" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B154,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B154,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N154" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B154,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B154,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O154" s="8">
@@ -17279,6 +19702,25 @@
           <t>153-zonneplein.jpg</t>
         </is>
       </c>
+      <c r="Z154" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn; het rapport noemt wel de asfaltsoort maar niet de uitvoering</t>
+        </is>
+      </c>
+      <c r="AA154" s="9" t="inlineStr"/>
+      <c r="AB154" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ZONNEPLEIN</t>
+        </is>
+      </c>
+      <c r="AC154" s="2" t="inlineStr">
+        <is>
+          <t>zwart (rijweg)</t>
+        </is>
+      </c>
+      <c r="AD154" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -17320,7 +19762,7 @@
         <v>5.48</v>
       </c>
       <c r="K155" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B155,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B155,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L155" s="7">
@@ -17328,11 +19770,11 @@
         <v/>
       </c>
       <c r="M155" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B155,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B155,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N155" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B155,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B155,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O155" s="8">
@@ -17381,6 +19823,21 @@
         <is>
           <t>154-zuideinde.jpg</t>
         </is>
+      </c>
+      <c r="Z155" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA155" s="9" t="inlineStr"/>
+      <c r="AB155" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-ZUIDEINDE</t>
+        </is>
+      </c>
+      <c r="AC155" s="2" t="inlineStr"/>
+      <c r="AD155" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -17413,7 +19870,7 @@
       <c r="I156" s="7" t="n"/>
       <c r="J156" s="7" t="n"/>
       <c r="K156" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B156,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B156,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L156" s="7">
@@ -17421,11 +19878,11 @@
         <v/>
       </c>
       <c r="M156" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B156,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B156,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N156" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B156,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B156,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O156" s="8">
@@ -17475,6 +19932,25 @@
           <t>155-schellingwouderdijk.jpg</t>
         </is>
       </c>
+      <c r="Z156" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA156" s="9" t="inlineStr">
+        <is>
+          <t>geen maatvoering in de bron</t>
+        </is>
+      </c>
+      <c r="AB156" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-SCHELLINGWOUDERDIJK</t>
+        </is>
+      </c>
+      <c r="AC156" s="2" t="inlineStr"/>
+      <c r="AD156" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -17516,7 +19992,7 @@
         <v>1.15</v>
       </c>
       <c r="K157" s="2">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B157,Tarieven!$A$4:$A$9,0),2)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B157,Tarieven!$A$4:$A$7,0),2)</f>
         <v/>
       </c>
       <c r="L157" s="7">
@@ -17524,11 +20000,11 @@
         <v/>
       </c>
       <c r="M157" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B157,Tarieven!$A$4:$A$9,0),3)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B157,Tarieven!$A$4:$A$7,0),3)</f>
         <v/>
       </c>
       <c r="N157" s="8">
-        <f>INDEX(Tarieven!$A$4:$E$9,MATCH($B157,Tarieven!$A$4:$A$9,0),4)</f>
+        <f>INDEX(Tarieven!$A$4:$E$7,MATCH($B157,Tarieven!$A$4:$A$7,0),4)</f>
         <v/>
       </c>
       <c r="O157" s="8">
@@ -17578,6 +20054,21 @@
           <t>156-volendammerweg.jpg</t>
         </is>
       </c>
+      <c r="Z157" s="9" t="inlineStr">
+        <is>
+          <t>geen code in de kantlijn en geen asfaltsoort in de tekst</t>
+        </is>
+      </c>
+      <c r="AA157" s="9" t="inlineStr"/>
+      <c r="AB157" s="2" t="inlineStr">
+        <is>
+          <t>SOK-AMS-VOLENDAMMERWEG</t>
+        </is>
+      </c>
+      <c r="AC157" s="2" t="inlineStr"/>
+      <c r="AD157" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -17585,27 +20076,27 @@
           <t>Totaal</t>
         </is>
       </c>
-      <c r="G159" s="9">
+      <c r="G159" s="10">
         <f>SUM(G2:G157)</f>
         <v/>
       </c>
-      <c r="H159" s="9">
+      <c r="H159" s="10">
         <f>SUM(H2:H157)</f>
         <v/>
       </c>
-      <c r="J159" s="9">
+      <c r="J159" s="10">
         <f>SUM(J2:J157)</f>
         <v/>
       </c>
-      <c r="L159" s="9">
+      <c r="L159" s="10">
         <f>SUM(L2:L157)</f>
         <v/>
       </c>
-      <c r="O159" s="10">
+      <c r="O159" s="11">
         <f>SUM(O2:O157)</f>
         <v/>
       </c>
-      <c r="P159" s="10">
+      <c r="P159" s="11">
         <f>SUM(P2:P157)</f>
         <v/>
       </c>
@@ -17621,7 +20112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -17773,7 +20264,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Asfalt zwart (rijweg)</t>
+          <t>Asfalt – nog in te delen</t>
         </is>
       </c>
       <c r="B7" s="2">
@@ -17802,95 +20293,33 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Asfalt rood (fiets-/voetpad)</t>
-        </is>
-      </c>
-      <c r="B8" s="2">
-        <f>COUNTIF(Locaties!$B$2:$B$157,$A8)</f>
-        <v/>
-      </c>
-      <c r="C8" s="7">
-        <f>SUMIF(Locaties!$B$2:$B$157,$A8,Locaties!$G$2:$G$157)</f>
-        <v/>
-      </c>
-      <c r="D8" s="7">
-        <f>SUMIF(Locaties!$B$2:$B$157,$A8,Locaties!$H$2:$H$157)</f>
-        <v/>
-      </c>
-      <c r="E8" s="7">
-        <f>SUMIF(Locaties!$B$2:$B$157,$A8,Locaties!$J$2:$J$157)</f>
-        <v/>
-      </c>
-      <c r="F8" s="8">
-        <f>SUMIF(Locaties!$B$2:$B$157,$A8,Locaties!$O$2:$O$157)</f>
-        <v/>
-      </c>
-      <c r="G8" s="8">
-        <f>SUMIF(Locaties!$B$2:$B$157,$A8,Locaties!$P$2:$P$157)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Asfalt – nog in te delen</t>
-        </is>
-      </c>
-      <c r="B9" s="2">
-        <f>COUNTIF(Locaties!$B$2:$B$157,$A9)</f>
-        <v/>
-      </c>
-      <c r="C9" s="7">
-        <f>SUMIF(Locaties!$B$2:$B$157,$A9,Locaties!$G$2:$G$157)</f>
-        <v/>
-      </c>
-      <c r="D9" s="7">
-        <f>SUMIF(Locaties!$B$2:$B$157,$A9,Locaties!$H$2:$H$157)</f>
-        <v/>
-      </c>
-      <c r="E9" s="7">
-        <f>SUMIF(Locaties!$B$2:$B$157,$A9,Locaties!$J$2:$J$157)</f>
-        <v/>
-      </c>
-      <c r="F9" s="8">
-        <f>SUMIF(Locaties!$B$2:$B$157,$A9,Locaties!$O$2:$O$157)</f>
-        <v/>
-      </c>
-      <c r="G9" s="8">
-        <f>SUMIF(Locaties!$B$2:$B$157,$A9,Locaties!$P$2:$P$157)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Totaal</t>
         </is>
       </c>
-      <c r="B10" s="9">
-        <f>SUM(B4:B9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="9">
-        <f>SUM(C4:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="9">
-        <f>SUM(D4:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="9">
-        <f>SUM(E4:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="10">
-        <f>SUM(F4:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="10">
-        <f>SUM(G4:G9)</f>
+      <c r="B8" s="10">
+        <f>SUM(B4:B7)</f>
+        <v/>
+      </c>
+      <c r="C8" s="10">
+        <f>SUM(C4:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="10">
+        <f>SUM(D4:D7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="10">
+        <f>SUM(E4:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="11">
+        <f>SUM(F4:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="11">
+        <f>SUM(G4:G7)</f>
         <v/>
       </c>
     </row>
@@ -17900,6 +20329,182 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rood asfalt tegenover zwart asfalt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Het bronrapport noemt de asfaltsoort alleen bij de herstelpunten van de nutsbedrijven. Bij de rest staat het er niet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Asfaltsoort</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Aantal locaties</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Oppervlak (m2)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Kosten min</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Kosten max</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>zwart (rijweg)</t>
+        </is>
+      </c>
+      <c r="B5" s="2">
+        <f>COUNTIF(Locaties!$AC$2:$AC$157,$A5)</f>
+        <v/>
+      </c>
+      <c r="C5" s="12">
+        <f>IFERROR($B5/$B$8,0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="7">
+        <f>SUMIF(Locaties!$AC$2:$AC$157,$A5,Locaties!$J$2:$J$157)</f>
+        <v/>
+      </c>
+      <c r="E5" s="8">
+        <f>SUMIF(Locaties!$AC$2:$AC$157,$A5,Locaties!$O$2:$O$157)</f>
+        <v/>
+      </c>
+      <c r="F5" s="8">
+        <f>SUMIF(Locaties!$AC$2:$AC$157,$A5,Locaties!$P$2:$P$157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>rood (fiets-/voetpad)</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <f>COUNTIF(Locaties!$AC$2:$AC$157,$A6)</f>
+        <v/>
+      </c>
+      <c r="C6" s="12">
+        <f>IFERROR($B6/$B$8,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="7">
+        <f>SUMIF(Locaties!$AC$2:$AC$157,$A6,Locaties!$J$2:$J$157)</f>
+        <v/>
+      </c>
+      <c r="E6" s="8">
+        <f>SUMIF(Locaties!$AC$2:$AC$157,$A6,Locaties!$O$2:$O$157)</f>
+        <v/>
+      </c>
+      <c r="F6" s="8">
+        <f>SUMIF(Locaties!$AC$2:$AC$157,$A6,Locaties!$P$2:$P$157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>niet vermeld in het rapport</t>
+        </is>
+      </c>
+      <c r="B7" s="2">
+        <f>$B$8-SUM(B5:B6)</f>
+        <v/>
+      </c>
+      <c r="C7" s="12">
+        <f>IFERROR($B7/$B$8,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="7">
+        <f>SUM(Locaties!$J$2:$J$157)-SUM(D5:D6)</f>
+        <v/>
+      </c>
+      <c r="E7" s="8">
+        <f>SUM(Locaties!$O$2:$O$157)-SUM(E5:E6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="8">
+        <f>SUM(Locaties!$P$2:$P$157)-SUM(F5:F6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Totaal (alle locaties)</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>COUNTA(Locaties!$A$2:$A$157)</f>
+        <v/>
+      </c>
+      <c r="C8" s="13">
+        <f>SUM(C5:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="10">
+        <f>SUM(Locaties!$J$2:$J$157)</f>
+        <v/>
+      </c>
+      <c r="E8" s="11">
+        <f>SUM(Locaties!$O$2:$O$157)</f>
+        <v/>
+      </c>
+      <c r="F8" s="11">
+        <f>SUM(Locaties!$P$2:$P$157)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19455,19 +22060,19 @@
           <t>Totaal</t>
         </is>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="10">
         <f>SUM(C4:C51)</f>
         <v/>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="10">
         <f>SUM(D4:D51)</f>
         <v/>
       </c>
-      <c r="E52" s="10">
+      <c r="E52" s="11">
         <f>SUM(E4:E51)</f>
         <v/>
       </c>
-      <c r="F52" s="10">
+      <c r="F52" s="11">
         <f>SUM(F4:F51)</f>
         <v/>
       </c>

--- a/data/SOK-Amsterdam-Asfalt-2026-calculatie.xlsx
+++ b/data/SOK-Amsterdam-Asfalt-2026-calculatie.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Locaties" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Per werksoort" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Per asfaltsoort" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Per weg" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Per klasse" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Per weg" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
@@ -635,66 +636,70 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Foto's</t>
+          <t>Schadebeeld, ernst en conditie</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>De foto's komen uit het digitale rapport, niet uit de scan. Waar de schouwer meer dan een</t>
+          <t>De foto's laten zien dat het meeste werk geen asfaltschade is maar elementenverharding</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>foto maakte staan ze allemaal in een genummerd blad, in dezelfde volgorde als zijn tekst</t>
+          <t>in het asfalt: klinkerstroken en -vlakken waar een sleuf heeft gelegen, die vervangen</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>('foto 1', 'foto 3'). Kolom 'Aantal foto's' zegt hoeveel opnames er per locatie zijn.</t>
+          <t>moeten worden door asfalt. In CROW-termen is dat vlakheid/verzakking, geen scheurvorming.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Daarnaast een minderheid met echte asfaltschade: gaten, rafeling en langsscheuren.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Maatvoering</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Ernst is per melding van de schouwfoto afgelezen, omvang volgt uit de gemeten maat</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>De schouwer noteert vrij: '4.00 x 1.40 + 1.80 x 2.00', '2x 2.20 x 0.45', 'Lengte 3,05 Breedte 1,81'.</t>
+          <t>(&lt; 2 m2 = 1, 2-10 m2 = 2, &gt; 10 m2 = 3). Samen geven ze de CROW-klasse en daaruit volgt</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Alle varianten zijn omgerekend naar vlakken, en daaruit volgt het oppervlak.</t>
+          <t>de NEN 2767-conditie. Het is een schatting van achter een bureau om op te prioriteren —</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Gecontroleerd tegen de eigen totalen van het rapport: 5,5 m2 en 4,1 m2 komen exact uit.</t>
+          <t>geen inspectie op locatie, en geen basis voor een bestek. De laatste kolom op het blad</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>10 van de 156 meldingen noemen geen enkele maat; die hebben geen oppervlak.</t>
+          <t>Locaties zegt per regel waar de indeling vandaan komt.</t>
         </is>
       </c>
     </row>
@@ -704,95 +709,164 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Tarieven</t>
+          <t>Foto's</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>De blauwe cellen op het blad Tarieven zijn invoer — pas ze aan naar je eigen prijspeil.</t>
+          <t>De foto's komen uit het digitale rapport, niet uit de scan. Waar de schouwer meer dan een</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>De startwaarden zijn de CROW-kostenkengetallen uit crow_kosten.py en zijn een orde van</t>
+          <t>foto maakte staan ze allemaal in een genummerd blad, in dezelfde volgorde als zijn tekst</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>grootte, geen offerte. Alle bedragen in dit werkboek rekenen daarop door.</t>
+          <t>('foto 1', 'foto 3'). Kolom 'Aantal foto's' zegt hoeveel opnames er per locatie zijn.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Met de startwaarden komt het totaal uit tussen € 37.584 en € 89.568.</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Maatvoering</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Let op</t>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>De schouwer noteert vrij: '4.00 x 1.40 + 1.80 x 2.00', '2x 2.20 x 0.45', 'Lengte 3,05 Breedte 1,81'.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Kolom 'Let op' op het blad Locaties markeert elke regel die aandacht vraagt.</t>
+          <t>Alle varianten zijn omgerekend naar vlakken, en daaruit volgt het oppervlak.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Baanakkerspad heeft geen GPS in het bronrapport.</t>
+          <t>Gecontroleerd tegen de eigen totalen van het rapport: 5,5 m2 en 4,1 m2 komen exact uit.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Stellingweg: het adres in het rapport (Ceramiquelaan 723) ligt 3,4 km van de overige</t>
+          <t>10 van de 156 meldingen noemen geen enkele maat; die hebben geen oppervlak.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>punten op die straat — coordinaat controleren.</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Tarieven</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Bijwerken</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>De blauwe cellen op het blad Tarieven zijn invoer — pas ze aan naar je eigen prijspeil.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Dit werkboek is gegenereerd uit data/sok_amsterdam_asfalt_2026.json met</t>
+          <t>De startwaarden zijn de CROW-kostenkengetallen uit crow_kosten.py en zijn een orde van</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>grootte, geen offerte. Alle bedragen in dit werkboek rekenen daarop door.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Met de startwaarden komt het totaal uit tussen € 37.584 en € 89.568.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Let op</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Kolom 'Let op' op het blad Locaties markeert elke regel die aandacht vraagt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Baanakkerspad heeft geen GPS in het bronrapport.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Stellingweg: het adres in het rapport (Ceramiquelaan 723) ligt 3,4 km van de overige</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>punten op die straat — coordinaat controleren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Bijwerken</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Dit werkboek is gegenereerd uit data/sok_amsterdam_asfalt_2026.json met</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>scripts/maak_calculatie_excel.py. Verandert de dataset, draai dat script opnieuw.</t>
         </is>
@@ -963,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD159"/>
+  <dimension ref="A1:AK159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -996,6 +1070,13 @@
     <col width="26" customWidth="1" min="28" max="28"/>
     <col width="22" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="42" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="20" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="17" customWidth="1" min="35" max="35"/>
+    <col width="26" customWidth="1" min="36" max="36"/>
+    <col width="54" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1149,6 +1230,41 @@
           <t>Aantal foto's</t>
         </is>
       </c>
+      <c r="AE1" s="6" t="inlineStr">
+        <is>
+          <t>Schadebeeld</t>
+        </is>
+      </c>
+      <c r="AF1" s="6" t="inlineStr">
+        <is>
+          <t>Ernst</t>
+        </is>
+      </c>
+      <c r="AG1" s="6" t="inlineStr">
+        <is>
+          <t>Omvang</t>
+        </is>
+      </c>
+      <c r="AH1" s="6" t="inlineStr">
+        <is>
+          <t>CROW-klasse</t>
+        </is>
+      </c>
+      <c r="AI1" s="6" t="inlineStr">
+        <is>
+          <t>NEN 2767 conditie</t>
+        </is>
+      </c>
+      <c r="AJ1" s="6" t="inlineStr">
+        <is>
+          <t>Onderhoud</t>
+        </is>
+      </c>
+      <c r="AK1" s="6" t="inlineStr">
+        <is>
+          <t>Waar komt de classificatie vandaan</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1271,6 +1387,39 @@
       <c r="AD2" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1392,6 +1541,39 @@
       <c r="AC3" s="2" t="inlineStr"/>
       <c r="AD3" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK3" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1509,6 +1691,39 @@
       <c r="AD4" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel); geen maat in de bron — omvang op het laagste niveau gezet</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1631,6 +1846,39 @@
       <c r="AD5" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK5" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1749,6 +1997,39 @@
       <c r="AD6" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK6" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1871,6 +2152,39 @@
       <c r="AD7" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH7" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK7" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1989,6 +2303,39 @@
       <c r="AD8" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH8" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK8" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2107,6 +2454,39 @@
       <c r="AD9" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH9" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK9" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2229,6 +2609,39 @@
       <c r="AD10" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK10" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2351,6 +2764,39 @@
       <c r="AD11" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ11" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2473,6 +2919,39 @@
       <c r="AD12" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ12" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2595,6 +3074,39 @@
       <c r="AD13" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ13" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2717,6 +3229,39 @@
       <c r="AD14" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ14" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2839,6 +3384,39 @@
       <c r="AD15" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ15" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2961,6 +3539,39 @@
       <c r="AD16" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ16" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3083,6 +3694,39 @@
       <c r="AD17" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE17" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH17" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ17" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3205,6 +3849,39 @@
       <c r="AD18" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE18" s="2" t="inlineStr">
+        <is>
+          <t>rafeling van de deklaag</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH18" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="AI18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ18" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3327,6 +4004,39 @@
       <c r="AD19" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE19" s="2" t="inlineStr">
+        <is>
+          <t>gaten in het asfalt</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="inlineStr">
+        <is>
+          <t>ernstig</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH19" s="2" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="AI19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ19" s="2" t="inlineStr">
+        <is>
+          <t>acuut — veiligheidsmaatregel</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3449,6 +4159,39 @@
       <c r="AD20" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE20" s="2" t="inlineStr">
+        <is>
+          <t>gaten in het asfalt</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="inlineStr">
+        <is>
+          <t>ernstig</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="AI20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ20" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3570,6 +4313,39 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="n">
         <v>2</v>
+      </c>
+      <c r="AE21" s="2" t="inlineStr">
+        <is>
+          <t>randschade / scheur langs de kant</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH21" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ21" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -3687,6 +4463,39 @@
       <c r="AD22" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE22" s="2" t="inlineStr">
+        <is>
+          <t>randschade / scheur langs de kant</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH22" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ22" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto; geen maat in de bron — omvang op het laagste niveau gezet</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3809,6 +4618,39 @@
       <c r="AD23" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE23" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ23" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3930,6 +4772,39 @@
       <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="AE24" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG24" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH24" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ24" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -4047,6 +4922,39 @@
       <c r="AD25" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE25" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG25" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH25" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ25" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel); geen maat in de bron — omvang op het laagste niveau gezet</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4169,6 +5077,39 @@
       <c r="AD26" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE26" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG26" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ26" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -4291,6 +5232,39 @@
       <c r="AD27" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE27" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG27" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH27" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="AI27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ27" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4413,6 +5387,39 @@
       <c r="AD28" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE28" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF28" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ28" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -4535,6 +5542,39 @@
       <c r="AD29" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF29" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ29" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -4657,6 +5697,39 @@
       <c r="AD30" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF30" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG30" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH30" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="AI30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ30" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -4779,6 +5852,39 @@
       <c r="AD31" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE31" s="2" t="inlineStr">
+        <is>
+          <t>gaten in het asfalt</t>
+        </is>
+      </c>
+      <c r="AF31" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG31" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH31" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ31" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -4901,6 +6007,39 @@
       <c r="AD32" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF32" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG32" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH32" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ32" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -5023,6 +6162,39 @@
       <c r="AD33" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF33" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG33" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH33" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ33" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK33" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -5145,6 +6317,39 @@
       <c r="AD34" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE34" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF34" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG34" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH34" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ34" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK34" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -5267,6 +6472,39 @@
       <c r="AD35" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE35" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF35" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG35" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH35" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ35" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK35" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -5388,6 +6626,39 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="AE36" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF36" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG36" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH36" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ36" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK36" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -5505,6 +6776,39 @@
       <c r="AD37" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE37" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF37" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG37" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH37" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ37" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK37" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel); geen maat in de bron — omvang op het laagste niveau gezet</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -5627,6 +6931,39 @@
       <c r="AD38" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE38" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF38" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG38" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH38" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ38" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK38" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -5749,6 +7086,39 @@
       <c r="AD39" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE39" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF39" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG39" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH39" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="AI39" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ39" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK39" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -5871,6 +7241,39 @@
       <c r="AD40" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE40" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF40" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG40" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH40" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ40" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK40" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -5993,6 +7396,39 @@
       <c r="AD41" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE41" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF41" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG41" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH41" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ41" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK41" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -6115,6 +7551,39 @@
       <c r="AD42" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE42" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF42" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG42" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH42" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="AI42" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ42" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK42" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -6237,6 +7706,39 @@
       <c r="AD43" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE43" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF43" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG43" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH43" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ43" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK43" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -6359,6 +7861,39 @@
       <c r="AD44" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE44" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF44" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG44" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH44" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ44" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK44" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -6481,6 +8016,39 @@
       <c r="AD45" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE45" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF45" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG45" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH45" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="AI45" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ45" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK45" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -6603,6 +8171,39 @@
       <c r="AD46" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE46" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF46" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG46" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH46" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ46" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK46" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -6725,6 +8326,39 @@
       <c r="AD47" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE47" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF47" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG47" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH47" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ47" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK47" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -6847,6 +8481,39 @@
       <c r="AD48" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE48" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF48" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG48" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH48" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ48" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK48" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -6969,6 +8636,39 @@
       <c r="AD49" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE49" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF49" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG49" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH49" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ49" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK49" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -7091,6 +8791,39 @@
       <c r="AD50" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE50" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF50" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG50" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH50" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ50" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK50" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -7213,6 +8946,39 @@
       <c r="AD51" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE51" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF51" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG51" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH51" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ51" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK51" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -7335,6 +9101,39 @@
       <c r="AD52" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE52" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF52" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG52" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH52" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ52" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK52" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -7457,6 +9256,39 @@
       <c r="AD53" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE53" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF53" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG53" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH53" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ53" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK53" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -7579,6 +9411,39 @@
       <c r="AD54" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE54" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF54" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG54" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH54" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ54" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK54" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -7701,6 +9566,39 @@
       <c r="AD55" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE55" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF55" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG55" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH55" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="AI55" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ55" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK55" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -7823,6 +9721,39 @@
       <c r="AD56" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE56" s="2" t="inlineStr">
+        <is>
+          <t>oneffen verharding</t>
+        </is>
+      </c>
+      <c r="AF56" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG56" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH56" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ56" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK56" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -7945,6 +9876,39 @@
       <c r="AD57" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE57" s="2" t="inlineStr">
+        <is>
+          <t>rafeling van de deklaag</t>
+        </is>
+      </c>
+      <c r="AF57" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG57" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH57" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI57" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ57" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK57" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -8067,6 +10031,39 @@
       <c r="AD58" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE58" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF58" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG58" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH58" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ58" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK58" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -8189,6 +10186,39 @@
       <c r="AD59" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE59" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF59" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG59" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH59" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ59" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK59" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -8311,6 +10341,39 @@
       <c r="AD60" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE60" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF60" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG60" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH60" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ60" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK60" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -8433,6 +10496,39 @@
       <c r="AD61" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE61" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF61" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG61" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH61" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI61" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ61" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK61" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -8555,6 +10651,39 @@
       <c r="AD62" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE62" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF62" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG62" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH62" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI62" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ62" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK62" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -8677,6 +10806,39 @@
       <c r="AD63" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE63" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF63" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG63" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH63" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ63" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK63" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -8799,6 +10961,39 @@
       <c r="AD64" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE64" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF64" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG64" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH64" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI64" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ64" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK64" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -8921,6 +11116,39 @@
       <c r="AD65" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE65" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF65" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG65" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH65" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI65" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ65" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK65" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -9043,6 +11271,39 @@
       <c r="AD66" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE66" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF66" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG66" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH66" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI66" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ66" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK66" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -9165,6 +11426,39 @@
       <c r="AD67" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE67" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF67" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG67" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH67" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI67" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ67" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK67" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -9283,6 +11577,39 @@
       <c r="AD68" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE68" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF68" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG68" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH68" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ68" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK68" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -9405,6 +11732,39 @@
       <c r="AD69" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE69" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF69" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG69" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH69" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI69" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ69" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK69" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -9527,6 +11887,39 @@
       <c r="AD70" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE70" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF70" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG70" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH70" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI70" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ70" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK70" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -9645,6 +12038,39 @@
       <c r="AD71" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE71" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF71" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG71" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH71" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI71" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ71" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK71" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -9767,6 +12193,39 @@
       <c r="AD72" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE72" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF72" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG72" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH72" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI72" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ72" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK72" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -9889,6 +12348,39 @@
       <c r="AD73" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE73" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF73" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG73" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH73" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI73" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ73" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK73" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -10011,6 +12503,39 @@
       <c r="AD74" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE74" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF74" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG74" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH74" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI74" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ74" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK74" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -10133,6 +12658,39 @@
       <c r="AD75" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE75" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF75" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG75" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH75" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI75" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ75" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK75" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -10255,6 +12813,39 @@
       <c r="AD76" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE76" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF76" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG76" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH76" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI76" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ76" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK76" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -10377,6 +12968,39 @@
       <c r="AD77" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE77" s="2" t="inlineStr">
+        <is>
+          <t>randschade / scheur langs de kant</t>
+        </is>
+      </c>
+      <c r="AF77" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG77" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH77" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI77" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ77" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK77" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -10499,6 +13123,39 @@
       <c r="AD78" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE78" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF78" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG78" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH78" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI78" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ78" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK78" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -10621,6 +13278,39 @@
       <c r="AD79" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE79" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF79" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG79" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH79" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI79" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ79" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK79" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -10743,6 +13433,39 @@
       <c r="AD80" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE80" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF80" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG80" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH80" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI80" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ80" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK80" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -10865,6 +13588,39 @@
       <c r="AD81" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE81" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF81" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG81" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH81" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI81" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ81" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK81" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -10987,6 +13743,39 @@
       <c r="AD82" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE82" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF82" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG82" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH82" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ82" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK82" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -11109,6 +13898,39 @@
       <c r="AD83" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE83" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF83" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG83" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH83" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ83" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK83" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -11231,6 +14053,39 @@
       <c r="AD84" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE84" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF84" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG84" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH84" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ84" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK84" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -11353,6 +14208,39 @@
       <c r="AD85" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE85" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF85" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG85" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH85" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI85" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ85" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK85" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -11475,6 +14363,39 @@
       <c r="AD86" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE86" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF86" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG86" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH86" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ86" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK86" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -11597,6 +14518,39 @@
       <c r="AD87" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE87" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF87" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG87" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH87" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI87" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ87" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK87" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -11719,6 +14673,39 @@
       <c r="AD88" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE88" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF88" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG88" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH88" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI88" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ88" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK88" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -11841,6 +14828,39 @@
       <c r="AD89" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE89" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF89" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG89" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH89" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI89" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ89" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK89" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -11962,6 +14982,39 @@
       <c r="AC90" s="2" t="inlineStr"/>
       <c r="AD90" s="2" t="n">
         <v>2</v>
+      </c>
+      <c r="AE90" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF90" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG90" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH90" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="AI90" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ90" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK90" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -12079,6 +15132,39 @@
       <c r="AD91" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE91" s="2" t="inlineStr">
+        <is>
+          <t>langsscheur</t>
+        </is>
+      </c>
+      <c r="AF91" s="2" t="inlineStr">
+        <is>
+          <t>ernstig</t>
+        </is>
+      </c>
+      <c r="AG91" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH91" s="2" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="AI91" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ91" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK91" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto; geen maat in de bron — omvang op het laagste niveau gezet</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -12195,6 +15281,39 @@
       <c r="AD92" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE92" s="2" t="inlineStr">
+        <is>
+          <t>rafeling van de deklaag</t>
+        </is>
+      </c>
+      <c r="AF92" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG92" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH92" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI92" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ92" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK92" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto; geen maat in de bron — omvang op het laagste niveau gezet</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -12317,6 +15436,39 @@
       <c r="AD93" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE93" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF93" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG93" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH93" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI93" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ93" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK93" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -12439,6 +15591,39 @@
       <c r="AD94" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE94" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF94" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG94" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH94" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI94" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ94" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK94" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -12561,6 +15746,39 @@
       <c r="AD95" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="AE95" s="2" t="inlineStr">
+        <is>
+          <t>rafeling van de deklaag</t>
+        </is>
+      </c>
+      <c r="AF95" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG95" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH95" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="AI95" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ95" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK95" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -12683,6 +15901,39 @@
       <c r="AD96" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE96" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF96" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG96" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH96" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI96" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ96" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK96" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -12805,6 +16056,39 @@
       <c r="AD97" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE97" s="2" t="inlineStr">
+        <is>
+          <t>gaten in het asfalt</t>
+        </is>
+      </c>
+      <c r="AF97" s="2" t="inlineStr">
+        <is>
+          <t>ernstig</t>
+        </is>
+      </c>
+      <c r="AG97" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH97" s="2" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="AI97" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ97" s="2" t="inlineStr">
+        <is>
+          <t>acuut — veiligheidsmaatregel</t>
+        </is>
+      </c>
+      <c r="AK97" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -12927,6 +16211,39 @@
       <c r="AD98" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE98" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF98" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG98" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH98" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI98" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ98" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK98" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -13049,6 +16366,39 @@
       <c r="AD99" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE99" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF99" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG99" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH99" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI99" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ99" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK99" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -13171,6 +16521,39 @@
       <c r="AD100" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE100" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF100" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG100" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH100" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="AI100" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ100" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK100" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -13293,6 +16676,39 @@
       <c r="AD101" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE101" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF101" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG101" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH101" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI101" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ101" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK101" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -13415,6 +16831,39 @@
       <c r="AD102" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE102" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF102" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG102" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH102" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI102" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ102" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK102" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -13537,6 +16986,39 @@
       <c r="AD103" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE103" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF103" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG103" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH103" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI103" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ103" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK103" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -13659,6 +17141,39 @@
       <c r="AD104" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE104" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF104" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG104" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH104" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI104" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ104" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK104" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -13781,6 +17296,39 @@
       <c r="AD105" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE105" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF105" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG105" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH105" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI105" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ105" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK105" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -13903,6 +17451,39 @@
       <c r="AD106" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE106" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF106" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG106" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH106" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI106" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ106" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK106" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -14025,6 +17606,39 @@
       <c r="AD107" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE107" s="2" t="inlineStr">
+        <is>
+          <t>gaten in het asfalt</t>
+        </is>
+      </c>
+      <c r="AF107" s="2" t="inlineStr">
+        <is>
+          <t>ernstig</t>
+        </is>
+      </c>
+      <c r="AG107" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH107" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="AI107" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ107" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK107" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -14147,6 +17761,39 @@
       <c r="AD108" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE108" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF108" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG108" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH108" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI108" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ108" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK108" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -14269,6 +17916,39 @@
       <c r="AD109" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE109" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF109" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG109" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH109" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI109" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ109" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK109" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -14391,6 +18071,39 @@
       <c r="AD110" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE110" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF110" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG110" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH110" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI110" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ110" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK110" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -14513,6 +18226,39 @@
       <c r="AD111" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE111" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF111" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG111" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH111" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI111" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ111" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK111" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -14635,6 +18381,39 @@
       <c r="AD112" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE112" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF112" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG112" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH112" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI112" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ112" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK112" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -14757,6 +18536,39 @@
       <c r="AD113" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE113" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF113" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG113" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH113" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI113" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ113" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK113" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -14879,6 +18691,39 @@
       <c r="AD114" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE114" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF114" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG114" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH114" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI114" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ114" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK114" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -15001,6 +18846,39 @@
       <c r="AD115" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE115" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF115" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG115" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH115" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI115" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ115" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK115" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -15123,6 +19001,39 @@
       <c r="AD116" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE116" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF116" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG116" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH116" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI116" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ116" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK116" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -15245,6 +19156,39 @@
       <c r="AD117" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="AE117" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF117" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG117" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH117" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI117" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ117" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK117" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -15367,6 +19311,39 @@
       <c r="AD118" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE118" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF118" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG118" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH118" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI118" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ118" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK118" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -15489,6 +19466,39 @@
       <c r="AD119" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE119" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF119" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG119" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH119" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI119" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ119" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK119" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -15611,6 +19621,39 @@
       <c r="AD120" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE120" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF120" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG120" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH120" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI120" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ120" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK120" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -15733,6 +19776,39 @@
       <c r="AD121" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE121" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF121" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG121" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH121" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI121" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ121" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK121" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -15855,6 +19931,39 @@
       <c r="AD122" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE122" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF122" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG122" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH122" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI122" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ122" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK122" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -15977,6 +20086,39 @@
       <c r="AD123" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE123" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF123" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG123" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH123" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI123" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ123" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK123" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -16099,6 +20241,39 @@
       <c r="AD124" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE124" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF124" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG124" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH124" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI124" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ124" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK124" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -16221,6 +20396,39 @@
       <c r="AD125" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE125" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF125" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG125" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH125" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI125" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ125" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK125" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -16343,6 +20551,39 @@
       <c r="AD126" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE126" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF126" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG126" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH126" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI126" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ126" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK126" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -16465,6 +20706,39 @@
       <c r="AD127" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE127" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF127" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG127" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH127" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI127" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ127" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK127" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -16587,6 +20861,39 @@
       <c r="AD128" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE128" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF128" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG128" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH128" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ128" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK128" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -16709,6 +21016,39 @@
       <c r="AD129" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE129" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF129" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG129" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH129" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI129" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ129" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK129" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -16831,6 +21171,39 @@
       <c r="AD130" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE130" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF130" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG130" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH130" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI130" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ130" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK130" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -16952,6 +21325,39 @@
       <c r="AC131" s="2" t="inlineStr"/>
       <c r="AD131" s="2" t="n">
         <v>2</v>
+      </c>
+      <c r="AE131" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF131" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG131" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH131" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="AI131" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ131" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK131" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -17069,6 +21475,39 @@
       <c r="AD132" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE132" s="2" t="inlineStr">
+        <is>
+          <t>langsscheur</t>
+        </is>
+      </c>
+      <c r="AF132" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG132" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH132" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI132" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ132" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK132" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto; geen maat in de bron — omvang op het laagste niveau gezet</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -17191,6 +21630,39 @@
       <c r="AD133" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE133" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF133" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG133" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH133" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI133" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ133" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK133" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -17313,6 +21785,39 @@
       <c r="AD134" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE134" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF134" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG134" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH134" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI134" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ134" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK134" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -17435,6 +21940,39 @@
       <c r="AD135" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE135" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF135" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG135" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH135" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI135" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ135" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK135" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -17557,6 +22095,39 @@
       <c r="AD136" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AE136" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF136" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG136" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH136" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AI136" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ136" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK136" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -17678,6 +22249,39 @@
       <c r="AC137" s="2" t="inlineStr"/>
       <c r="AD137" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="AE137" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF137" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG137" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH137" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AI137" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ137" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK137" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -17791,6 +22395,39 @@
       <c r="AD138" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="AE138" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF138" s="2" t="inlineStr">
+        <is>
+          <t>ernstig</t>
+        </is>
+      </c>
+      <c r="AG138" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH138" s="2" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="AI138" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ138" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK138" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto; geen maat in de bron — omvang op het laagste niveau gezet</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -17913,6 +22550,39 @@
       <c r="AD139" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE139" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF139" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG139" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH139" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI139" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ139" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK139" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -18035,6 +22705,39 @@
       <c r="AD140" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE140" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF140" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG140" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH140" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="AI140" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ140" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK140" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (zichtbaar verzakt of begroeid)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -18157,6 +22860,39 @@
       <c r="AD141" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AE141" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF141" s="2" t="inlineStr">
+        <is>
+          <t>gering</t>
+        </is>
+      </c>
+      <c r="AG141" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH141" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="AI141" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ141" s="2" t="inlineStr">
+        <is>
+          <t>observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="AK141" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto (klinkerstrook ligt heel)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -18278,6 +23014,39 @@
       <c r="AC142" s="2" t="inlineStr"/>
       <c r="AD142" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="AE142" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF142" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG142" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH142" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI142" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ142" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK142" s="2" t="inlineStr">
+        <is>
+          <t>sleufherstel van een nutsbedrijf — tijdelijke dichtzetting in de rijbaan</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -18393,6 +23162,39 @@
       <c r="AD143" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE143" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF143" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG143" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH143" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI143" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ143" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK143" s="2" t="inlineStr">
+        <is>
+          <t>sleufherstel van een nutsbedrijf — tijdelijke dichtzetting in de rijbaan</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -18514,6 +23316,39 @@
       </c>
       <c r="AD144" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="AE144" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF144" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG144" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH144" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="AI144" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ144" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK144" s="2" t="inlineStr">
+        <is>
+          <t>sleufherstel van een nutsbedrijf — tijdelijke dichtzetting in de rijbaan</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -18632,6 +23467,39 @@
       <c r="AC145" s="2" t="inlineStr"/>
       <c r="AD145" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="AE145" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF145" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG145" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH145" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI145" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ145" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK145" s="2" t="inlineStr">
+        <is>
+          <t>sleufherstel van een nutsbedrijf — tijdelijke dichtzetting in de rijbaan</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -18745,6 +23613,39 @@
       <c r="AD146" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE146" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF146" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG146" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH146" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI146" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ146" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK146" s="2" t="inlineStr">
+        <is>
+          <t>sleufherstel van een nutsbedrijf — tijdelijke dichtzetting in de rijbaan; geen maat in de bron — omvang op het laagste niveau gezet</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -18867,6 +23768,39 @@
       <c r="AD147" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE147" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF147" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG147" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH147" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI147" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ147" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK147" s="2" t="inlineStr">
+        <is>
+          <t>sleufherstel van een nutsbedrijf — tijdelijke dichtzetting in de rijbaan</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -18989,6 +23923,39 @@
       <c r="AD148" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE148" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF148" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG148" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH148" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ148" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK148" s="2" t="inlineStr">
+        <is>
+          <t>sleufherstel van een nutsbedrijf — tijdelijke dichtzetting in de rijbaan</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -19111,6 +24078,39 @@
       <c r="AD149" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE149" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF149" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG149" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH149" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI149" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ149" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK149" s="2" t="inlineStr">
+        <is>
+          <t>sleufherstel van een nutsbedrijf — tijdelijke dichtzetting in de rijbaan</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -19233,6 +24233,39 @@
       <c r="AD150" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE150" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF150" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG150" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH150" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI150" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ150" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK150" s="2" t="inlineStr">
+        <is>
+          <t>sleufherstel van een nutsbedrijf — tijdelijke dichtzetting in de rijbaan</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -19355,6 +24388,39 @@
       <c r="AD151" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE151" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF151" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG151" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH151" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI151" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ151" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK151" s="2" t="inlineStr">
+        <is>
+          <t>sleufherstel van een nutsbedrijf — tijdelijke dichtzetting in de rijbaan</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -19477,6 +24543,39 @@
       <c r="AD152" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE152" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF152" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG152" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH152" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI152" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ152" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK152" s="2" t="inlineStr">
+        <is>
+          <t>sleufherstel van een nutsbedrijf — tijdelijke dichtzetting in de rijbaan</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -19599,6 +24698,39 @@
       <c r="AD153" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE153" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF153" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG153" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH153" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI153" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ153" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK153" s="2" t="inlineStr">
+        <is>
+          <t>sleufherstel van een nutsbedrijf — tijdelijke dichtzetting in de rijbaan</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -19720,6 +24852,39 @@
       </c>
       <c r="AD154" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="AE154" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF154" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG154" s="2" t="inlineStr">
+        <is>
+          <t>groot (&gt; 10 m2)</t>
+        </is>
+      </c>
+      <c r="AH154" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="AI154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ154" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK154" s="2" t="inlineStr">
+        <is>
+          <t>sleufherstel van een nutsbedrijf — tijdelijke dichtzetting in de rijbaan</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -19838,6 +25003,39 @@
       <c r="AC155" s="2" t="inlineStr"/>
       <c r="AD155" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="AE155" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF155" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG155" s="2" t="inlineStr">
+        <is>
+          <t>gemiddeld (2-10 m2)</t>
+        </is>
+      </c>
+      <c r="AH155" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="AI155" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ155" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK155" s="2" t="inlineStr">
+        <is>
+          <t>sleufherstel van een nutsbedrijf — tijdelijke dichtzetting in de rijbaan</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -19951,6 +25149,39 @@
       <c r="AD156" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AE156" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF156" s="2" t="inlineStr">
+        <is>
+          <t>serieus</t>
+        </is>
+      </c>
+      <c r="AG156" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH156" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AI156" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ156" s="2" t="inlineStr">
+        <is>
+          <t>klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="AK156" s="2" t="inlineStr">
+        <is>
+          <t>sleufherstel van een nutsbedrijf — tijdelijke dichtzetting in de rijbaan; geen maat in de bron — omvang op het laagste niveau gezet</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -20068,6 +25299,39 @@
       <c r="AC157" s="2" t="inlineStr"/>
       <c r="AD157" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="AE157" s="2" t="inlineStr">
+        <is>
+          <t>verzakte elementenverharding (klinkerstrook in het asfalt)</t>
+        </is>
+      </c>
+      <c r="AF157" s="2" t="inlineStr">
+        <is>
+          <t>ernstig</t>
+        </is>
+      </c>
+      <c r="AG157" s="2" t="inlineStr">
+        <is>
+          <t>beperkt (&lt; 2 m2)</t>
+        </is>
+      </c>
+      <c r="AH157" s="2" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="AI157" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ157" s="2" t="inlineStr">
+        <is>
+          <t>groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="AK157" s="2" t="inlineStr">
+        <is>
+          <t>afgelezen van de schouwfoto</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -20510,6 +25774,349 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ernst en omvang — CROW-klasse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ernst is afgelezen van de schouwfoto, omvang volgt uit de gemeten maat. Een schatting om op te prioriteren — controleren op locatie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CROW-klasse</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Betekenis</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Aantal locaties</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Oppervlak (m2)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Kosten min</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Kosten max</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>gering, beperkt (&lt; 2 m2) — observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="C5" s="2">
+        <f>COUNTIF(Locaties!$AH$2:$AH$157,$A5)</f>
+        <v/>
+      </c>
+      <c r="D5" s="7">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A5,Locaties!$J$2:$J$157)</f>
+        <v/>
+      </c>
+      <c r="E5" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A5,Locaties!$O$2:$O$157)</f>
+        <v/>
+      </c>
+      <c r="F5" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A5,Locaties!$P$2:$P$157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>gering, gemiddeld (2-10 m2) — observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="C6" s="2">
+        <f>COUNTIF(Locaties!$AH$2:$AH$157,$A6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="7">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A6,Locaties!$J$2:$J$157)</f>
+        <v/>
+      </c>
+      <c r="E6" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A6,Locaties!$O$2:$O$157)</f>
+        <v/>
+      </c>
+      <c r="F6" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A6,Locaties!$P$2:$P$157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>gering, groot (&gt; 10 m2) — observatie — volgende schouw</t>
+        </is>
+      </c>
+      <c r="C7" s="2">
+        <f>COUNTIF(Locaties!$AH$2:$AH$157,$A7)</f>
+        <v/>
+      </c>
+      <c r="D7" s="7">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A7,Locaties!$J$2:$J$157)</f>
+        <v/>
+      </c>
+      <c r="E7" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A7,Locaties!$O$2:$O$157)</f>
+        <v/>
+      </c>
+      <c r="F7" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A7,Locaties!$P$2:$P$157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>serieus, beperkt (&lt; 2 m2) — klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="C8" s="2">
+        <f>COUNTIF(Locaties!$AH$2:$AH$157,$A8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="7">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A8,Locaties!$J$2:$J$157)</f>
+        <v/>
+      </c>
+      <c r="E8" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A8,Locaties!$O$2:$O$157)</f>
+        <v/>
+      </c>
+      <c r="F8" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A8,Locaties!$P$2:$P$157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>serieus, gemiddeld (2-10 m2) — klein onderhoud — binnen het jaar</t>
+        </is>
+      </c>
+      <c r="C9" s="2">
+        <f>COUNTIF(Locaties!$AH$2:$AH$157,$A9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="7">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A9,Locaties!$J$2:$J$157)</f>
+        <v/>
+      </c>
+      <c r="E9" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A9,Locaties!$O$2:$O$157)</f>
+        <v/>
+      </c>
+      <c r="F9" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A9,Locaties!$P$2:$P$157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>serieus, groot (&gt; 10 m2) — groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="C10" s="2">
+        <f>COUNTIF(Locaties!$AH$2:$AH$157,$A10)</f>
+        <v/>
+      </c>
+      <c r="D10" s="7">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A10,Locaties!$J$2:$J$157)</f>
+        <v/>
+      </c>
+      <c r="E10" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A10,Locaties!$O$2:$O$157)</f>
+        <v/>
+      </c>
+      <c r="F10" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A10,Locaties!$P$2:$P$157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>ernstig, beperkt (&lt; 2 m2) — groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="C11" s="2">
+        <f>COUNTIF(Locaties!$AH$2:$AH$157,$A11)</f>
+        <v/>
+      </c>
+      <c r="D11" s="7">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A11,Locaties!$J$2:$J$157)</f>
+        <v/>
+      </c>
+      <c r="E11" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A11,Locaties!$O$2:$O$157)</f>
+        <v/>
+      </c>
+      <c r="F11" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A11,Locaties!$P$2:$P$157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ernstig, gemiddeld (2-10 m2) — groot onderhoud — inplannen</t>
+        </is>
+      </c>
+      <c r="C12" s="2">
+        <f>COUNTIF(Locaties!$AH$2:$AH$157,$A12)</f>
+        <v/>
+      </c>
+      <c r="D12" s="7">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A12,Locaties!$J$2:$J$157)</f>
+        <v/>
+      </c>
+      <c r="E12" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A12,Locaties!$O$2:$O$157)</f>
+        <v/>
+      </c>
+      <c r="F12" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A12,Locaties!$P$2:$P$157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ernstig, groot (&gt; 10 m2) — acuut — veiligheidsmaatregel</t>
+        </is>
+      </c>
+      <c r="C13" s="2">
+        <f>COUNTIF(Locaties!$AH$2:$AH$157,$A13)</f>
+        <v/>
+      </c>
+      <c r="D13" s="7">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A13,Locaties!$J$2:$J$157)</f>
+        <v/>
+      </c>
+      <c r="E13" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A13,Locaties!$O$2:$O$157)</f>
+        <v/>
+      </c>
+      <c r="F13" s="8">
+        <f>SUMIF(Locaties!$AH$2:$AH$157,$A13,Locaties!$P$2:$P$157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Totaal</t>
+        </is>
+      </c>
+      <c r="C14" s="10">
+        <f>SUM(C5:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="10">
+        <f>SUM(D5:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="11">
+        <f>SUM(E5:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="11">
+        <f>SUM(F5:F13)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
